--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555AC293-0F2D-45BE-9557-FA989AD859E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAA6034-F266-46B5-9B81-BDCF017F552B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -4123,11 +4123,14 @@
       </c>
       <c r="H46" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1045.png</v>
       </c>
       <c r="I46" t="str">
         <f t="shared" si="1"/>
         <v/>
+      </c>
+      <c r="J46">
+        <v>1</v>
       </c>
       <c r="L46">
         <f t="shared" si="2"/>
@@ -4510,11 +4513,14 @@
       </c>
       <c r="H58" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1057.png</v>
       </c>
       <c r="I58" t="str">
         <f t="shared" si="1"/>
         <v/>
+      </c>
+      <c r="J58">
+        <v>1</v>
       </c>
       <c r="L58">
         <f t="shared" si="2"/>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAA6034-F266-46B5-9B81-BDCF017F552B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D1B76D-1537-491F-91EE-93CE0E4F07FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -3924,18 +3924,21 @@
         <v>26</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="F40" t="s">
         <v>369</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1039.png</v>
       </c>
       <c r="I40" t="str">
         <f t="shared" si="1"/>
         <v/>
+      </c>
+      <c r="J40">
+        <v>1</v>
       </c>
       <c r="L40">
         <f t="shared" si="2"/>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D1B76D-1537-491F-91EE-93CE0E4F07FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE520E0C-F7FE-4A48-9F4F-6AD5E15BFD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -1304,10 +1304,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>떠아콩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>케이대</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2245,10 +2241,6 @@
     <t>jooyoung0040</t>
   </si>
   <si>
-    <t>또아임니더</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1004yomi</t>
   </si>
   <si>
@@ -2273,6 +2265,14 @@
   </si>
   <si>
     <t>넘버링</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>떠아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>또아</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2673,22 +2673,22 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>626</v>
+      </c>
+      <c r="H1" t="s">
+        <v>627</v>
+      </c>
+      <c r="I1" t="s">
         <v>628</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>629</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>630</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>631</v>
-      </c>
-      <c r="K1" t="s">
-        <v>632</v>
-      </c>
-      <c r="L1" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.6">
@@ -2708,10 +2708,10 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G2" s="1">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="H2" t="str">
         <f>IF(J2=1,L2&amp;".png","")</f>
@@ -2743,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" ref="H3:H66" si="0">IF(J3=1,L3&amp;".png","")</f>
@@ -2775,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
@@ -2798,7 +2798,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -2807,7 +2807,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
@@ -2839,7 +2839,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
@@ -2871,7 +2871,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
@@ -2894,7 +2894,7 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -2903,7 +2903,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="0"/>
@@ -2926,7 +2926,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -2935,7 +2935,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" si="0"/>
@@ -2958,7 +2958,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -2967,7 +2967,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H10" t="str">
         <f t="shared" si="0"/>
@@ -2990,7 +2990,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
@@ -2999,7 +2999,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="0"/>
@@ -3031,7 +3031,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" si="0"/>
@@ -3063,7 +3063,7 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="0"/>
@@ -3086,7 +3086,7 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
@@ -3095,7 +3095,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H14" t="str">
         <f t="shared" si="0"/>
@@ -3127,7 +3127,7 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H15" t="str">
         <f t="shared" si="0"/>
@@ -3159,7 +3159,7 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H16" t="str">
         <f t="shared" si="0"/>
@@ -3191,7 +3191,7 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H17" t="str">
         <f t="shared" si="0"/>
@@ -3223,7 +3223,7 @@
         <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H18" t="str">
         <f t="shared" si="0"/>
@@ -3255,7 +3255,7 @@
         <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="0"/>
@@ -3278,7 +3278,7 @@
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -3287,7 +3287,7 @@
         <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H20" t="str">
         <f t="shared" si="0"/>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H21" t="str">
         <f t="shared" si="0"/>
@@ -3342,7 +3342,7 @@
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -3351,7 +3351,7 @@
         <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H22" t="str">
         <f t="shared" si="0"/>
@@ -3383,7 +3383,7 @@
         <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H23" t="str">
         <f t="shared" si="0"/>
@@ -3415,7 +3415,7 @@
         <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H24" t="str">
         <f t="shared" si="0"/>
@@ -3438,7 +3438,7 @@
         <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -3447,7 +3447,7 @@
         <v>27</v>
       </c>
       <c r="F25" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="0"/>
@@ -3479,7 +3479,7 @@
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H26" t="str">
         <f t="shared" si="0"/>
@@ -3511,7 +3511,7 @@
         <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H27" t="str">
         <f t="shared" si="0"/>
@@ -3543,7 +3543,7 @@
         <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H28" t="str">
         <f t="shared" si="0"/>
@@ -3575,7 +3575,7 @@
         <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H29" t="str">
         <f t="shared" si="0"/>
@@ -3607,7 +3607,7 @@
         <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H30" t="str">
         <f t="shared" si="0"/>
@@ -3630,7 +3630,7 @@
         <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
@@ -3639,7 +3639,7 @@
         <v>27</v>
       </c>
       <c r="F31" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="0"/>
@@ -3662,7 +3662,7 @@
         <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D32" t="s">
         <v>21</v>
@@ -3671,7 +3671,7 @@
         <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H32" t="str">
         <f t="shared" si="0"/>
@@ -3694,7 +3694,7 @@
         <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D33" t="s">
         <v>21</v>
@@ -3703,7 +3703,7 @@
         <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H33" t="str">
         <f t="shared" si="0"/>
@@ -3726,7 +3726,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
@@ -3735,7 +3735,7 @@
         <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H34" t="str">
         <f t="shared" si="0"/>
@@ -3758,7 +3758,7 @@
         <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D35" t="s">
         <v>21</v>
@@ -3767,7 +3767,7 @@
         <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H35" t="str">
         <f t="shared" si="0"/>
@@ -3790,7 +3790,7 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D36" t="s">
         <v>26</v>
@@ -3799,7 +3799,7 @@
         <v>27</v>
       </c>
       <c r="F36" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="0"/>
@@ -3831,7 +3831,7 @@
         <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H37" t="str">
         <f t="shared" si="0"/>
@@ -3863,7 +3863,7 @@
         <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H38" t="str">
         <f t="shared" si="0"/>
@@ -3895,7 +3895,7 @@
         <v>27</v>
       </c>
       <c r="F39" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" si="0"/>
@@ -3918,7 +3918,7 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D40" t="s">
         <v>26</v>
@@ -3927,7 +3927,7 @@
         <v>62</v>
       </c>
       <c r="F40" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" si="0"/>
@@ -3962,7 +3962,7 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H41" t="str">
         <f t="shared" si="0"/>
@@ -3994,7 +3994,7 @@
         <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H42" t="str">
         <f t="shared" si="0"/>
@@ -4017,7 +4017,7 @@
         <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
@@ -4026,7 +4026,7 @@
         <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H43" t="str">
         <f t="shared" si="0"/>
@@ -4058,7 +4058,7 @@
         <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H44" t="str">
         <f t="shared" si="0"/>
@@ -4090,7 +4090,7 @@
         <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H45" t="str">
         <f t="shared" si="0"/>
@@ -4113,7 +4113,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -4122,7 +4122,7 @@
         <v>62</v>
       </c>
       <c r="F46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H46" t="str">
         <f t="shared" si="0"/>
@@ -4157,7 +4157,7 @@
         <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H47" t="str">
         <f t="shared" si="0"/>
@@ -4180,7 +4180,7 @@
         <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -4189,7 +4189,7 @@
         <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H48" t="str">
         <f t="shared" si="0"/>
@@ -4212,7 +4212,7 @@
         <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -4221,7 +4221,7 @@
         <v>62</v>
       </c>
       <c r="F49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H49" t="str">
         <f t="shared" si="0"/>
@@ -4253,7 +4253,7 @@
         <v>62</v>
       </c>
       <c r="F50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H50" t="str">
         <f t="shared" si="0"/>
@@ -4285,7 +4285,7 @@
         <v>62</v>
       </c>
       <c r="F51" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H51" t="str">
         <f t="shared" si="0"/>
@@ -4308,7 +4308,7 @@
         <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D52" t="s">
         <v>21</v>
@@ -4317,7 +4317,7 @@
         <v>62</v>
       </c>
       <c r="F52" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H52" t="str">
         <f t="shared" si="0"/>
@@ -4352,7 +4352,7 @@
         <v>62</v>
       </c>
       <c r="F53" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H53" t="str">
         <f t="shared" si="0"/>
@@ -4384,7 +4384,7 @@
         <v>62</v>
       </c>
       <c r="F54" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H54" t="str">
         <f t="shared" si="0"/>
@@ -4407,7 +4407,7 @@
         <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D55" t="s">
         <v>21</v>
@@ -4416,7 +4416,7 @@
         <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H55" t="str">
         <f t="shared" si="0"/>
@@ -4439,7 +4439,7 @@
         <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D56" t="s">
         <v>21</v>
@@ -4448,7 +4448,7 @@
         <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H56" t="str">
         <f t="shared" si="0"/>
@@ -4480,7 +4480,7 @@
         <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H57" t="str">
         <f t="shared" si="0"/>
@@ -4503,7 +4503,7 @@
         <v>69</v>
       </c>
       <c r="C58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D58" t="s">
         <v>21</v>
@@ -4512,7 +4512,7 @@
         <v>62</v>
       </c>
       <c r="F58" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H58" t="str">
         <f t="shared" si="0"/>
@@ -4547,7 +4547,7 @@
         <v>62</v>
       </c>
       <c r="F59" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H59" t="str">
         <f t="shared" si="0"/>
@@ -4579,7 +4579,7 @@
         <v>62</v>
       </c>
       <c r="F60" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H60" t="str">
         <f t="shared" si="0"/>
@@ -4611,7 +4611,7 @@
         <v>62</v>
       </c>
       <c r="F61" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H61" t="str">
         <f t="shared" si="0"/>
@@ -4634,7 +4634,7 @@
         <v>73</v>
       </c>
       <c r="C62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D62" t="s">
         <v>21</v>
@@ -4643,7 +4643,7 @@
         <v>62</v>
       </c>
       <c r="F62" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H62" t="str">
         <f t="shared" si="0"/>
@@ -4675,7 +4675,7 @@
         <v>62</v>
       </c>
       <c r="F63" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H63" t="str">
         <f t="shared" si="0"/>
@@ -4698,7 +4698,7 @@
         <v>75</v>
       </c>
       <c r="C64" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D64" t="s">
         <v>21</v>
@@ -4707,7 +4707,7 @@
         <v>62</v>
       </c>
       <c r="F64" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H64" t="str">
         <f t="shared" si="0"/>
@@ -4730,7 +4730,7 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D65" t="s">
         <v>21</v>
@@ -4739,7 +4739,7 @@
         <v>62</v>
       </c>
       <c r="F65" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H65" t="str">
         <f t="shared" si="0"/>
@@ -4771,7 +4771,7 @@
         <v>62</v>
       </c>
       <c r="F66" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H66" t="str">
         <f t="shared" si="0"/>
@@ -4803,7 +4803,7 @@
         <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H67" t="str">
         <f t="shared" ref="H67:H130" si="3">IF(J67=1,L67&amp;".png","")</f>
@@ -4826,7 +4826,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D68" t="s">
         <v>26</v>
@@ -4835,7 +4835,7 @@
         <v>62</v>
       </c>
       <c r="F68" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H68" t="str">
         <f t="shared" si="3"/>
@@ -4867,7 +4867,7 @@
         <v>62</v>
       </c>
       <c r="F69" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H69" t="str">
         <f t="shared" si="3"/>
@@ -4899,7 +4899,7 @@
         <v>62</v>
       </c>
       <c r="F70" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H70" t="str">
         <f t="shared" si="3"/>
@@ -4931,7 +4931,7 @@
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H71" t="str">
         <f t="shared" si="3"/>
@@ -4963,7 +4963,7 @@
         <v>62</v>
       </c>
       <c r="F72" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H72" t="str">
         <f t="shared" si="3"/>
@@ -4986,7 +4986,7 @@
         <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D73" t="s">
         <v>26</v>
@@ -4995,7 +4995,7 @@
         <v>62</v>
       </c>
       <c r="F73" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H73" t="str">
         <f t="shared" si="3"/>
@@ -5027,7 +5027,7 @@
         <v>62</v>
       </c>
       <c r="F74" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H74" t="str">
         <f t="shared" si="3"/>
@@ -5059,7 +5059,7 @@
         <v>62</v>
       </c>
       <c r="F75" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H75" t="str">
         <f t="shared" si="3"/>
@@ -5082,7 +5082,7 @@
         <v>87</v>
       </c>
       <c r="C76" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D76" t="s">
         <v>26</v>
@@ -5091,7 +5091,7 @@
         <v>62</v>
       </c>
       <c r="F76" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H76" t="str">
         <f t="shared" si="3"/>
@@ -5114,7 +5114,7 @@
         <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5123,7 +5123,7 @@
         <v>90</v>
       </c>
       <c r="F77" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H77" t="str">
         <f t="shared" si="3"/>
@@ -5155,7 +5155,7 @@
         <v>90</v>
       </c>
       <c r="F78" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H78" t="str">
         <f t="shared" si="3"/>
@@ -5178,7 +5178,7 @@
         <v>91</v>
       </c>
       <c r="C79" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5187,7 +5187,7 @@
         <v>90</v>
       </c>
       <c r="F79" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H79" t="str">
         <f t="shared" si="3"/>
@@ -5219,7 +5219,7 @@
         <v>90</v>
       </c>
       <c r="F80" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H80" t="str">
         <f t="shared" si="3"/>
@@ -5242,7 +5242,7 @@
         <v>93</v>
       </c>
       <c r="C81" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D81" t="s">
         <v>21</v>
@@ -5251,7 +5251,7 @@
         <v>90</v>
       </c>
       <c r="F81" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H81" t="str">
         <f t="shared" si="3"/>
@@ -5274,7 +5274,7 @@
         <v>94</v>
       </c>
       <c r="C82" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D82" t="s">
         <v>21</v>
@@ -5283,7 +5283,7 @@
         <v>90</v>
       </c>
       <c r="F82" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H82" t="str">
         <f t="shared" si="3"/>
@@ -5306,7 +5306,7 @@
         <v>95</v>
       </c>
       <c r="C83" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D83" t="s">
         <v>21</v>
@@ -5315,7 +5315,7 @@
         <v>90</v>
       </c>
       <c r="F83" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H83" t="str">
         <f t="shared" si="3"/>
@@ -5338,7 +5338,7 @@
         <v>96</v>
       </c>
       <c r="C84" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D84" t="s">
         <v>21</v>
@@ -5347,7 +5347,7 @@
         <v>90</v>
       </c>
       <c r="F84" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H84" t="str">
         <f t="shared" si="3"/>
@@ -5379,7 +5379,7 @@
         <v>90</v>
       </c>
       <c r="F85" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H85" t="str">
         <f t="shared" si="3"/>
@@ -5411,7 +5411,7 @@
         <v>90</v>
       </c>
       <c r="F86" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H86" t="str">
         <f t="shared" si="3"/>
@@ -5434,7 +5434,7 @@
         <v>99</v>
       </c>
       <c r="C87" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D87" t="s">
         <v>26</v>
@@ -5443,7 +5443,7 @@
         <v>90</v>
       </c>
       <c r="F87" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H87" t="str">
         <f t="shared" si="3"/>
@@ -5466,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D88" t="s">
         <v>26</v>
@@ -5475,7 +5475,7 @@
         <v>90</v>
       </c>
       <c r="F88" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H88" t="str">
         <f t="shared" si="3"/>
@@ -5498,7 +5498,7 @@
         <v>101</v>
       </c>
       <c r="C89" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D89" t="s">
         <v>26</v>
@@ -5507,7 +5507,7 @@
         <v>90</v>
       </c>
       <c r="F89" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H89" t="str">
         <f t="shared" si="3"/>
@@ -5539,7 +5539,7 @@
         <v>90</v>
       </c>
       <c r="F90" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H90" t="str">
         <f t="shared" si="3"/>
@@ -5571,7 +5571,7 @@
         <v>90</v>
       </c>
       <c r="F91" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H91" t="str">
         <f t="shared" si="3"/>
@@ -5594,7 +5594,7 @@
         <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D92" t="s">
         <v>26</v>
@@ -5603,7 +5603,7 @@
         <v>90</v>
       </c>
       <c r="F92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H92" t="str">
         <f t="shared" si="3"/>
@@ -5626,7 +5626,7 @@
         <v>105</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D93" t="s">
         <v>26</v>
@@ -5635,7 +5635,7 @@
         <v>90</v>
       </c>
       <c r="F93" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H93" t="str">
         <f t="shared" si="3"/>
@@ -5658,7 +5658,7 @@
         <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
@@ -5667,7 +5667,7 @@
         <v>90</v>
       </c>
       <c r="F94" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H94" t="str">
         <f t="shared" si="3"/>
@@ -5690,7 +5690,7 @@
         <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D95" t="s">
         <v>26</v>
@@ -5699,7 +5699,7 @@
         <v>90</v>
       </c>
       <c r="F95" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H95" t="str">
         <f t="shared" si="3"/>
@@ -5731,7 +5731,7 @@
         <v>90</v>
       </c>
       <c r="F96" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H96" t="str">
         <f t="shared" si="3"/>
@@ -5763,7 +5763,7 @@
         <v>90</v>
       </c>
       <c r="F97" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H97" t="str">
         <f t="shared" si="3"/>
@@ -5795,7 +5795,7 @@
         <v>110</v>
       </c>
       <c r="F98" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H98" t="str">
         <f t="shared" si="3"/>
@@ -5818,7 +5818,7 @@
         <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -5827,7 +5827,7 @@
         <v>110</v>
       </c>
       <c r="F99" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H99" t="str">
         <f t="shared" si="3"/>
@@ -5850,7 +5850,7 @@
         <v>113</v>
       </c>
       <c r="C100" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -5859,7 +5859,7 @@
         <v>110</v>
       </c>
       <c r="F100" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H100" t="str">
         <f t="shared" si="3"/>
@@ -5891,7 +5891,7 @@
         <v>110</v>
       </c>
       <c r="F101" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H101" t="str">
         <f t="shared" si="3"/>
@@ -5923,7 +5923,7 @@
         <v>110</v>
       </c>
       <c r="F102" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H102" t="str">
         <f t="shared" si="3"/>
@@ -5946,7 +5946,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D103" t="s">
         <v>21</v>
@@ -5955,7 +5955,7 @@
         <v>110</v>
       </c>
       <c r="F103" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H103" t="str">
         <f t="shared" si="3"/>
@@ -5987,7 +5987,7 @@
         <v>110</v>
       </c>
       <c r="F104" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H104" t="str">
         <f t="shared" si="3"/>
@@ -6010,7 +6010,7 @@
         <v>117</v>
       </c>
       <c r="C105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D105" t="s">
         <v>26</v>
@@ -6019,7 +6019,7 @@
         <v>110</v>
       </c>
       <c r="F105" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H105" t="str">
         <f t="shared" si="3"/>
@@ -6042,7 +6042,7 @@
         <v>118</v>
       </c>
       <c r="C106" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D106" t="s">
         <v>26</v>
@@ -6051,7 +6051,7 @@
         <v>110</v>
       </c>
       <c r="F106" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H106" t="str">
         <f t="shared" si="3"/>
@@ -6074,7 +6074,7 @@
         <v>119</v>
       </c>
       <c r="C107" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D107" t="s">
         <v>26</v>
@@ -6083,7 +6083,7 @@
         <v>110</v>
       </c>
       <c r="F107" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H107" t="str">
         <f t="shared" si="3"/>
@@ -6103,10 +6103,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C108" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D108" t="s">
         <v>26</v>
@@ -6115,7 +6115,7 @@
         <v>110</v>
       </c>
       <c r="F108" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H108" t="str">
         <f t="shared" si="3"/>
@@ -6138,7 +6138,7 @@
         <v>120</v>
       </c>
       <c r="C109" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -6147,7 +6147,7 @@
         <v>110</v>
       </c>
       <c r="F109" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H109" t="str">
         <f t="shared" si="3"/>
@@ -6170,7 +6170,7 @@
         <v>121</v>
       </c>
       <c r="C110" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D110" t="s">
         <v>26</v>
@@ -6179,7 +6179,7 @@
         <v>110</v>
       </c>
       <c r="F110" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H110" t="str">
         <f t="shared" si="3"/>
@@ -6202,7 +6202,7 @@
         <v>122</v>
       </c>
       <c r="C111" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
@@ -6211,7 +6211,7 @@
         <v>110</v>
       </c>
       <c r="F111" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H111" t="str">
         <f t="shared" si="3"/>
@@ -6234,7 +6234,7 @@
         <v>123</v>
       </c>
       <c r="C112" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D112" t="s">
         <v>26</v>
@@ -6243,7 +6243,7 @@
         <v>110</v>
       </c>
       <c r="F112" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H112" t="str">
         <f t="shared" si="3"/>
@@ -6266,7 +6266,7 @@
         <v>124</v>
       </c>
       <c r="C113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6275,7 +6275,7 @@
         <v>126</v>
       </c>
       <c r="F113" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H113" t="str">
         <f t="shared" si="3"/>
@@ -6307,7 +6307,7 @@
         <v>126</v>
       </c>
       <c r="F114" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H114" t="str">
         <f t="shared" si="3"/>
@@ -6330,7 +6330,7 @@
         <v>127</v>
       </c>
       <c r="C115" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D115" t="s">
         <v>21</v>
@@ -6339,7 +6339,7 @@
         <v>126</v>
       </c>
       <c r="F115" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H115" t="str">
         <f t="shared" si="3"/>
@@ -6371,7 +6371,7 @@
         <v>126</v>
       </c>
       <c r="F116" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H116" t="str">
         <f t="shared" si="3"/>
@@ -6394,7 +6394,7 @@
         <v>129</v>
       </c>
       <c r="C117" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D117" t="s">
         <v>26</v>
@@ -6403,7 +6403,7 @@
         <v>126</v>
       </c>
       <c r="F117" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H117" t="str">
         <f t="shared" si="3"/>
@@ -6426,7 +6426,7 @@
         <v>130</v>
       </c>
       <c r="C118" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D118" t="s">
         <v>26</v>
@@ -6435,7 +6435,7 @@
         <v>126</v>
       </c>
       <c r="F118" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H118" t="str">
         <f t="shared" si="3"/>
@@ -6458,7 +6458,7 @@
         <v>131</v>
       </c>
       <c r="C119" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D119" t="s">
         <v>26</v>
@@ -6467,7 +6467,7 @@
         <v>126</v>
       </c>
       <c r="F119" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H119" t="str">
         <f t="shared" si="3"/>
@@ -6490,7 +6490,7 @@
         <v>132</v>
       </c>
       <c r="C120" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -6499,7 +6499,7 @@
         <v>126</v>
       </c>
       <c r="F120" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H120" t="str">
         <f t="shared" si="3"/>
@@ -6522,7 +6522,7 @@
         <v>133</v>
       </c>
       <c r="C121" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D121" t="s">
         <v>26</v>
@@ -6531,7 +6531,7 @@
         <v>126</v>
       </c>
       <c r="F121" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H121" t="str">
         <f t="shared" si="3"/>
@@ -6554,7 +6554,7 @@
         <v>134</v>
       </c>
       <c r="C122" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6563,7 +6563,7 @@
         <v>137</v>
       </c>
       <c r="F122" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H122" t="str">
         <f t="shared" si="3"/>
@@ -6595,7 +6595,7 @@
         <v>137</v>
       </c>
       <c r="F123" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H123" t="str">
         <f t="shared" si="3"/>
@@ -6618,7 +6618,7 @@
         <v>136</v>
       </c>
       <c r="C124" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6627,7 +6627,7 @@
         <v>137</v>
       </c>
       <c r="F124" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H124" t="str">
         <f t="shared" si="3"/>
@@ -6650,7 +6650,7 @@
         <v>138</v>
       </c>
       <c r="C125" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D125" t="s">
         <v>26</v>
@@ -6659,7 +6659,7 @@
         <v>137</v>
       </c>
       <c r="F125" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H125" t="str">
         <f t="shared" si="3"/>
@@ -6682,7 +6682,7 @@
         <v>139</v>
       </c>
       <c r="C126" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D126" t="s">
         <v>26</v>
@@ -6691,7 +6691,7 @@
         <v>137</v>
       </c>
       <c r="F126" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H126" t="str">
         <f t="shared" si="3"/>
@@ -6723,7 +6723,7 @@
         <v>137</v>
       </c>
       <c r="F127" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H127" t="str">
         <f t="shared" si="3"/>
@@ -6746,7 +6746,7 @@
         <v>141</v>
       </c>
       <c r="C128" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6755,7 +6755,7 @@
         <v>144</v>
       </c>
       <c r="F128" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H128" t="str">
         <f t="shared" si="3"/>
@@ -6787,7 +6787,7 @@
         <v>144</v>
       </c>
       <c r="F129" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H129" t="str">
         <f t="shared" si="3"/>
@@ -6819,7 +6819,7 @@
         <v>144</v>
       </c>
       <c r="F130" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H130" t="str">
         <f t="shared" si="3"/>
@@ -6842,7 +6842,7 @@
         <v>145</v>
       </c>
       <c r="C131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D131" t="s">
         <v>21</v>
@@ -6851,7 +6851,7 @@
         <v>144</v>
       </c>
       <c r="F131" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H131" t="str">
         <f t="shared" ref="H131:H194" si="6">IF(J131=1,L131&amp;".png","")</f>
@@ -6883,7 +6883,7 @@
         <v>144</v>
       </c>
       <c r="F132" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H132" t="str">
         <f t="shared" si="6"/>
@@ -6915,7 +6915,7 @@
         <v>144</v>
       </c>
       <c r="F133" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H133" t="str">
         <f t="shared" si="6"/>
@@ -6938,7 +6938,7 @@
         <v>148</v>
       </c>
       <c r="C134" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D134" t="s">
         <v>21</v>
@@ -6947,7 +6947,7 @@
         <v>144</v>
       </c>
       <c r="F134" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H134" t="str">
         <f t="shared" si="6"/>
@@ -6979,7 +6979,7 @@
         <v>144</v>
       </c>
       <c r="F135" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H135" t="str">
         <f t="shared" si="6"/>
@@ -7011,7 +7011,7 @@
         <v>144</v>
       </c>
       <c r="F136" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H136" t="str">
         <f t="shared" si="6"/>
@@ -7031,7 +7031,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C137" t="s">
         <v>10</v>
@@ -7043,7 +7043,7 @@
         <v>144</v>
       </c>
       <c r="F137" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H137" t="str">
         <f t="shared" si="6"/>
@@ -7066,7 +7066,7 @@
         <v>151</v>
       </c>
       <c r="C138" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D138" t="s">
         <v>26</v>
@@ -7075,7 +7075,7 @@
         <v>144</v>
       </c>
       <c r="F138" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H138" t="str">
         <f t="shared" si="6"/>
@@ -7107,7 +7107,7 @@
         <v>172</v>
       </c>
       <c r="F139" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H139" t="str">
         <f t="shared" si="6"/>
@@ -7139,7 +7139,7 @@
         <v>172</v>
       </c>
       <c r="F140" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H140" t="str">
         <f t="shared" si="6"/>
@@ -7171,7 +7171,7 @@
         <v>172</v>
       </c>
       <c r="F141" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H141" t="str">
         <f t="shared" si="6"/>
@@ -7194,7 +7194,7 @@
         <v>155</v>
       </c>
       <c r="C142" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -7203,7 +7203,7 @@
         <v>172</v>
       </c>
       <c r="F142" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H142" t="str">
         <f t="shared" si="6"/>
@@ -7235,7 +7235,7 @@
         <v>172</v>
       </c>
       <c r="F143" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H143" t="str">
         <f t="shared" si="6"/>
@@ -7267,7 +7267,7 @@
         <v>172</v>
       </c>
       <c r="F144" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H144" t="str">
         <f t="shared" si="6"/>
@@ -7299,7 +7299,7 @@
         <v>172</v>
       </c>
       <c r="F145" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H145" t="str">
         <f t="shared" si="6"/>
@@ -7322,7 +7322,7 @@
         <v>159</v>
       </c>
       <c r="C146" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D146" t="s">
         <v>21</v>
@@ -7331,7 +7331,7 @@
         <v>172</v>
       </c>
       <c r="F146" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H146" t="str">
         <f t="shared" si="6"/>
@@ -7354,7 +7354,7 @@
         <v>160</v>
       </c>
       <c r="C147" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D147" t="s">
         <v>21</v>
@@ -7363,7 +7363,7 @@
         <v>172</v>
       </c>
       <c r="F147" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H147" t="str">
         <f t="shared" si="6"/>
@@ -7395,7 +7395,7 @@
         <v>172</v>
       </c>
       <c r="F148" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H148" t="str">
         <f t="shared" si="6"/>
@@ -7427,7 +7427,7 @@
         <v>172</v>
       </c>
       <c r="F149" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H149" t="str">
         <f t="shared" si="6"/>
@@ -7459,7 +7459,7 @@
         <v>172</v>
       </c>
       <c r="F150" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H150" t="str">
         <f t="shared" si="6"/>
@@ -7491,7 +7491,7 @@
         <v>172</v>
       </c>
       <c r="F151" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H151" t="str">
         <f t="shared" si="6"/>
@@ -7514,7 +7514,7 @@
         <v>165</v>
       </c>
       <c r="C152" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D152" t="s">
         <v>26</v>
@@ -7523,7 +7523,7 @@
         <v>172</v>
       </c>
       <c r="F152" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H152" t="str">
         <f t="shared" si="6"/>
@@ -7549,7 +7549,7 @@
         <v>166</v>
       </c>
       <c r="C153" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D153" t="s">
         <v>26</v>
@@ -7558,7 +7558,7 @@
         <v>172</v>
       </c>
       <c r="F153" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H153" t="str">
         <f t="shared" si="6"/>
@@ -7581,7 +7581,7 @@
         <v>167</v>
       </c>
       <c r="C154" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D154" t="s">
         <v>26</v>
@@ -7590,7 +7590,7 @@
         <v>172</v>
       </c>
       <c r="F154" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H154" t="str">
         <f t="shared" si="6"/>
@@ -7622,7 +7622,7 @@
         <v>172</v>
       </c>
       <c r="F155" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H155" t="str">
         <f t="shared" si="6"/>
@@ -7645,7 +7645,7 @@
         <v>169</v>
       </c>
       <c r="C156" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D156" t="s">
         <v>26</v>
@@ -7654,7 +7654,7 @@
         <v>172</v>
       </c>
       <c r="F156" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H156" t="str">
         <f t="shared" si="6"/>
@@ -7677,7 +7677,7 @@
         <v>170</v>
       </c>
       <c r="C157" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D157" t="s">
         <v>26</v>
@@ -7686,7 +7686,7 @@
         <v>172</v>
       </c>
       <c r="F157" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H157" t="str">
         <f t="shared" si="6"/>
@@ -7718,7 +7718,7 @@
         <v>172</v>
       </c>
       <c r="F158" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H158" t="str">
         <f t="shared" si="6"/>
@@ -7750,7 +7750,7 @@
         <v>184</v>
       </c>
       <c r="F159" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H159" t="str">
         <f t="shared" si="6"/>
@@ -7782,7 +7782,7 @@
         <v>184</v>
       </c>
       <c r="F160" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H160" t="str">
         <f t="shared" si="6"/>
@@ -7805,7 +7805,7 @@
         <v>175</v>
       </c>
       <c r="C161" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7814,7 +7814,7 @@
         <v>184</v>
       </c>
       <c r="F161" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H161" t="str">
         <f t="shared" si="6"/>
@@ -7837,7 +7837,7 @@
         <v>176</v>
       </c>
       <c r="C162" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D162" t="s">
         <v>21</v>
@@ -7846,7 +7846,7 @@
         <v>184</v>
       </c>
       <c r="F162" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H162" t="str">
         <f t="shared" si="6"/>
@@ -7869,7 +7869,7 @@
         <v>177</v>
       </c>
       <c r="C163" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D163" t="s">
         <v>21</v>
@@ -7878,7 +7878,7 @@
         <v>184</v>
       </c>
       <c r="F163" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H163" t="str">
         <f t="shared" si="6"/>
@@ -7901,7 +7901,7 @@
         <v>178</v>
       </c>
       <c r="C164" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D164" t="s">
         <v>21</v>
@@ -7910,7 +7910,7 @@
         <v>184</v>
       </c>
       <c r="F164" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H164" t="str">
         <f t="shared" si="6"/>
@@ -7933,7 +7933,7 @@
         <v>179</v>
       </c>
       <c r="C165" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D165" t="s">
         <v>21</v>
@@ -7942,7 +7942,7 @@
         <v>184</v>
       </c>
       <c r="F165" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H165" t="str">
         <f t="shared" si="6"/>
@@ -7974,7 +7974,7 @@
         <v>184</v>
       </c>
       <c r="F166" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H166" t="str">
         <f t="shared" si="6"/>
@@ -8006,7 +8006,7 @@
         <v>184</v>
       </c>
       <c r="F167" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H167" t="str">
         <f t="shared" si="6"/>
@@ -8029,7 +8029,7 @@
         <v>182</v>
       </c>
       <c r="C168" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D168" t="s">
         <v>21</v>
@@ -8038,7 +8038,7 @@
         <v>184</v>
       </c>
       <c r="F168" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H168" t="str">
         <f t="shared" si="6"/>
@@ -8061,7 +8061,7 @@
         <v>183</v>
       </c>
       <c r="C169" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D169" t="s">
         <v>21</v>
@@ -8070,7 +8070,7 @@
         <v>184</v>
       </c>
       <c r="F169" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H169" t="str">
         <f t="shared" si="6"/>
@@ -8093,7 +8093,7 @@
         <v>185</v>
       </c>
       <c r="C170" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D170" t="s">
         <v>26</v>
@@ -8102,7 +8102,7 @@
         <v>184</v>
       </c>
       <c r="F170" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H170" t="str">
         <f t="shared" si="6"/>
@@ -8125,7 +8125,7 @@
         <v>186</v>
       </c>
       <c r="C171" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D171" t="s">
         <v>26</v>
@@ -8134,7 +8134,7 @@
         <v>184</v>
       </c>
       <c r="F171" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H171" t="str">
         <f t="shared" si="6"/>
@@ -8166,7 +8166,7 @@
         <v>184</v>
       </c>
       <c r="F172" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H172" t="str">
         <f t="shared" si="6"/>
@@ -8189,7 +8189,7 @@
         <v>188</v>
       </c>
       <c r="C173" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D173" t="s">
         <v>26</v>
@@ -8198,7 +8198,7 @@
         <v>184</v>
       </c>
       <c r="F173" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H173" t="str">
         <f t="shared" si="6"/>
@@ -8230,7 +8230,7 @@
         <v>184</v>
       </c>
       <c r="F174" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H174" t="str">
         <f t="shared" si="6"/>
@@ -8253,7 +8253,7 @@
         <v>190</v>
       </c>
       <c r="C175" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -8262,7 +8262,7 @@
         <v>199</v>
       </c>
       <c r="F175" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H175" t="str">
         <f t="shared" si="6"/>
@@ -8294,7 +8294,7 @@
         <v>199</v>
       </c>
       <c r="F176" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H176" t="str">
         <f t="shared" si="6"/>
@@ -8317,7 +8317,7 @@
         <v>192</v>
       </c>
       <c r="C177" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -8326,7 +8326,7 @@
         <v>199</v>
       </c>
       <c r="F177" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H177" t="str">
         <f t="shared" si="6"/>
@@ -8349,7 +8349,7 @@
         <v>193</v>
       </c>
       <c r="C178" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -8358,7 +8358,7 @@
         <v>199</v>
       </c>
       <c r="F178" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H178" t="str">
         <f t="shared" si="6"/>
@@ -8381,7 +8381,7 @@
         <v>194</v>
       </c>
       <c r="C179" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -8390,7 +8390,7 @@
         <v>199</v>
       </c>
       <c r="F179" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H179" t="str">
         <f t="shared" si="6"/>
@@ -8413,7 +8413,7 @@
         <v>195</v>
       </c>
       <c r="C180" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -8422,7 +8422,7 @@
         <v>199</v>
       </c>
       <c r="F180" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H180" t="str">
         <f t="shared" si="6"/>
@@ -8445,7 +8445,7 @@
         <v>196</v>
       </c>
       <c r="C181" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -8454,7 +8454,7 @@
         <v>199</v>
       </c>
       <c r="F181" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H181" t="str">
         <f t="shared" si="6"/>
@@ -8486,7 +8486,7 @@
         <v>199</v>
       </c>
       <c r="F182" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H182" t="str">
         <f t="shared" si="6"/>
@@ -8518,7 +8518,7 @@
         <v>199</v>
       </c>
       <c r="F183" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H183" t="str">
         <f t="shared" si="6"/>
@@ -8541,7 +8541,7 @@
         <v>200</v>
       </c>
       <c r="C184" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D184" t="s">
         <v>21</v>
@@ -8550,7 +8550,7 @@
         <v>199</v>
       </c>
       <c r="F184" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H184" t="str">
         <f t="shared" si="6"/>
@@ -8582,7 +8582,7 @@
         <v>199</v>
       </c>
       <c r="F185" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H185" t="str">
         <f t="shared" si="6"/>
@@ -8614,7 +8614,7 @@
         <v>199</v>
       </c>
       <c r="F186" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H186" t="str">
         <f t="shared" si="6"/>
@@ -8637,7 +8637,7 @@
         <v>203</v>
       </c>
       <c r="C187" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D187" t="s">
         <v>21</v>
@@ -8646,7 +8646,7 @@
         <v>199</v>
       </c>
       <c r="F187" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H187" t="str">
         <f t="shared" si="6"/>
@@ -8669,7 +8669,7 @@
         <v>204</v>
       </c>
       <c r="C188" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D188" t="s">
         <v>21</v>
@@ -8678,7 +8678,7 @@
         <v>199</v>
       </c>
       <c r="F188" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H188" t="str">
         <f t="shared" si="6"/>
@@ -8701,7 +8701,7 @@
         <v>205</v>
       </c>
       <c r="C189" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D189" t="s">
         <v>21</v>
@@ -8710,7 +8710,7 @@
         <v>199</v>
       </c>
       <c r="F189" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H189" t="str">
         <f t="shared" si="6"/>
@@ -8733,7 +8733,7 @@
         <v>206</v>
       </c>
       <c r="C190" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D190" t="s">
         <v>21</v>
@@ -8742,7 +8742,7 @@
         <v>199</v>
       </c>
       <c r="F190" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H190" t="str">
         <f t="shared" si="6"/>
@@ -8765,7 +8765,7 @@
         <v>207</v>
       </c>
       <c r="C191" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D191" t="s">
         <v>26</v>
@@ -8774,7 +8774,7 @@
         <v>199</v>
       </c>
       <c r="F191" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H191" t="str">
         <f t="shared" si="6"/>
@@ -8797,7 +8797,7 @@
         <v>208</v>
       </c>
       <c r="C192" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D192" t="s">
         <v>26</v>
@@ -8806,7 +8806,7 @@
         <v>199</v>
       </c>
       <c r="F192" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H192" t="str">
         <f t="shared" si="6"/>
@@ -8838,7 +8838,7 @@
         <v>199</v>
       </c>
       <c r="F193" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H193" t="str">
         <f t="shared" si="6"/>
@@ -8861,7 +8861,7 @@
         <v>210</v>
       </c>
       <c r="C194" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D194" t="s">
         <v>26</v>
@@ -8870,7 +8870,7 @@
         <v>199</v>
       </c>
       <c r="F194" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H194" t="str">
         <f t="shared" si="6"/>
@@ -8893,7 +8893,7 @@
         <v>211</v>
       </c>
       <c r="C195" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D195" t="s">
         <v>26</v>
@@ -8902,7 +8902,7 @@
         <v>199</v>
       </c>
       <c r="F195" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H195" t="str">
         <f t="shared" ref="H195:H258" si="9">IF(J195=1,L195&amp;".png","")</f>
@@ -8925,7 +8925,7 @@
         <v>212</v>
       </c>
       <c r="C196" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D196" t="s">
         <v>26</v>
@@ -8934,7 +8934,7 @@
         <v>199</v>
       </c>
       <c r="F196" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H196" t="str">
         <f t="shared" si="9"/>
@@ -8957,7 +8957,7 @@
         <v>213</v>
       </c>
       <c r="C197" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D197" t="s">
         <v>26</v>
@@ -8966,7 +8966,7 @@
         <v>199</v>
       </c>
       <c r="F197" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H197" t="str">
         <f t="shared" si="9"/>
@@ -8989,7 +8989,7 @@
         <v>214</v>
       </c>
       <c r="C198" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D198" t="s">
         <v>26</v>
@@ -8998,7 +8998,7 @@
         <v>199</v>
       </c>
       <c r="F198" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H198" t="str">
         <f t="shared" si="9"/>
@@ -9030,7 +9030,7 @@
         <v>222</v>
       </c>
       <c r="F199" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H199" t="str">
         <f t="shared" si="9"/>
@@ -9062,7 +9062,7 @@
         <v>222</v>
       </c>
       <c r="F200" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H200" t="str">
         <f t="shared" si="9"/>
@@ -9094,7 +9094,7 @@
         <v>222</v>
       </c>
       <c r="F201" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H201" t="str">
         <f t="shared" si="9"/>
@@ -9117,7 +9117,7 @@
         <v>218</v>
       </c>
       <c r="C202" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -9126,7 +9126,7 @@
         <v>222</v>
       </c>
       <c r="F202" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H202" t="str">
         <f t="shared" si="9"/>
@@ -9149,7 +9149,7 @@
         <v>219</v>
       </c>
       <c r="C203" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -9158,7 +9158,7 @@
         <v>222</v>
       </c>
       <c r="F203" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H203" t="str">
         <f t="shared" si="9"/>
@@ -9193,7 +9193,7 @@
         <v>222</v>
       </c>
       <c r="F204" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H204" t="str">
         <f t="shared" si="9"/>
@@ -9225,7 +9225,7 @@
         <v>222</v>
       </c>
       <c r="F205" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H205" t="str">
         <f t="shared" si="9"/>
@@ -9248,7 +9248,7 @@
         <v>223</v>
       </c>
       <c r="C206" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D206" t="s">
         <v>21</v>
@@ -9257,7 +9257,7 @@
         <v>222</v>
       </c>
       <c r="F206" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H206" t="str">
         <f t="shared" si="9"/>
@@ -9280,7 +9280,7 @@
         <v>224</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D207" t="s">
         <v>21</v>
@@ -9289,7 +9289,7 @@
         <v>222</v>
       </c>
       <c r="F207" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H207" t="str">
         <f t="shared" si="9"/>
@@ -9321,7 +9321,7 @@
         <v>222</v>
       </c>
       <c r="F208" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H208" t="str">
         <f t="shared" si="9"/>
@@ -9344,7 +9344,7 @@
         <v>226</v>
       </c>
       <c r="C209" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D209" t="s">
         <v>21</v>
@@ -9353,7 +9353,7 @@
         <v>222</v>
       </c>
       <c r="F209" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H209" t="str">
         <f t="shared" si="9"/>
@@ -9376,7 +9376,7 @@
         <v>227</v>
       </c>
       <c r="C210" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D210" t="s">
         <v>21</v>
@@ -9385,7 +9385,7 @@
         <v>222</v>
       </c>
       <c r="F210" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H210" t="str">
         <f t="shared" si="9"/>
@@ -9417,7 +9417,7 @@
         <v>222</v>
       </c>
       <c r="F211" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H211" t="str">
         <f t="shared" si="9"/>
@@ -9449,7 +9449,7 @@
         <v>222</v>
       </c>
       <c r="F212" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H212" t="str">
         <f t="shared" si="9"/>
@@ -9472,7 +9472,7 @@
         <v>230</v>
       </c>
       <c r="C213" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D213" t="s">
         <v>21</v>
@@ -9481,7 +9481,7 @@
         <v>222</v>
       </c>
       <c r="F213" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H213" t="str">
         <f t="shared" si="9"/>
@@ -9513,7 +9513,7 @@
         <v>222</v>
       </c>
       <c r="F214" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H214" t="str">
         <f t="shared" si="9"/>
@@ -9536,7 +9536,7 @@
         <v>232</v>
       </c>
       <c r="C215" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D215" t="s">
         <v>21</v>
@@ -9545,7 +9545,7 @@
         <v>222</v>
       </c>
       <c r="F215" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H215" t="str">
         <f t="shared" si="9"/>
@@ -9577,7 +9577,7 @@
         <v>222</v>
       </c>
       <c r="F216" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H216" t="str">
         <f t="shared" si="9"/>
@@ -9600,7 +9600,7 @@
         <v>234</v>
       </c>
       <c r="C217" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D217" t="s">
         <v>26</v>
@@ -9609,7 +9609,7 @@
         <v>222</v>
       </c>
       <c r="F217" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H217" t="str">
         <f t="shared" si="9"/>
@@ -9632,7 +9632,7 @@
         <v>235</v>
       </c>
       <c r="C218" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D218" t="s">
         <v>26</v>
@@ -9641,7 +9641,7 @@
         <v>222</v>
       </c>
       <c r="F218" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H218" t="str">
         <f t="shared" si="9"/>
@@ -9664,7 +9664,7 @@
         <v>236</v>
       </c>
       <c r="C219" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D219" t="s">
         <v>26</v>
@@ -9673,7 +9673,7 @@
         <v>222</v>
       </c>
       <c r="F219" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H219" t="str">
         <f t="shared" si="9"/>
@@ -9705,7 +9705,7 @@
         <v>222</v>
       </c>
       <c r="F220" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H220" t="str">
         <f t="shared" si="9"/>
@@ -9737,7 +9737,7 @@
         <v>222</v>
       </c>
       <c r="F221" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H221" t="str">
         <f t="shared" si="9"/>
@@ -9760,7 +9760,7 @@
         <v>239</v>
       </c>
       <c r="C222" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D222" t="s">
         <v>26</v>
@@ -9769,7 +9769,7 @@
         <v>222</v>
       </c>
       <c r="F222" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H222" t="str">
         <f t="shared" si="9"/>
@@ -9801,7 +9801,7 @@
         <v>222</v>
       </c>
       <c r="F223" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H223" t="str">
         <f t="shared" si="9"/>
@@ -9833,7 +9833,7 @@
         <v>251</v>
       </c>
       <c r="F224" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H224" t="str">
         <f t="shared" si="9"/>
@@ -9865,7 +9865,7 @@
         <v>251</v>
       </c>
       <c r="F225" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H225" t="str">
         <f t="shared" si="9"/>
@@ -9888,7 +9888,7 @@
         <v>243</v>
       </c>
       <c r="C226" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -9897,7 +9897,7 @@
         <v>251</v>
       </c>
       <c r="F226" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H226" t="str">
         <f t="shared" si="9"/>
@@ -9929,7 +9929,7 @@
         <v>251</v>
       </c>
       <c r="F227" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H227" t="str">
         <f t="shared" si="9"/>
@@ -9961,7 +9961,7 @@
         <v>251</v>
       </c>
       <c r="F228" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H228" t="str">
         <f t="shared" si="9"/>
@@ -9984,7 +9984,7 @@
         <v>246</v>
       </c>
       <c r="C229" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -9993,7 +9993,7 @@
         <v>251</v>
       </c>
       <c r="F229" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H229" t="str">
         <f t="shared" si="9"/>
@@ -10016,7 +10016,7 @@
         <v>247</v>
       </c>
       <c r="C230" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -10025,7 +10025,7 @@
         <v>251</v>
       </c>
       <c r="F230" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H230" t="str">
         <f t="shared" si="9"/>
@@ -10057,7 +10057,7 @@
         <v>251</v>
       </c>
       <c r="F231" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H231" t="str">
         <f t="shared" si="9"/>
@@ -10080,7 +10080,7 @@
         <v>249</v>
       </c>
       <c r="C232" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>251</v>
       </c>
       <c r="F232" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H232" t="str">
         <f t="shared" si="9"/>
@@ -10121,7 +10121,7 @@
         <v>251</v>
       </c>
       <c r="F233" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H233" t="str">
         <f t="shared" si="9"/>
@@ -10144,7 +10144,7 @@
         <v>252</v>
       </c>
       <c r="C234" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D234" t="s">
         <v>21</v>
@@ -10153,7 +10153,7 @@
         <v>251</v>
       </c>
       <c r="F234" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H234" t="str">
         <f t="shared" si="9"/>
@@ -10176,7 +10176,7 @@
         <v>253</v>
       </c>
       <c r="C235" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D235" t="s">
         <v>21</v>
@@ -10185,7 +10185,7 @@
         <v>251</v>
       </c>
       <c r="F235" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H235" t="str">
         <f t="shared" si="9"/>
@@ -10208,7 +10208,7 @@
         <v>254</v>
       </c>
       <c r="C236" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D236" t="s">
         <v>21</v>
@@ -10217,7 +10217,7 @@
         <v>251</v>
       </c>
       <c r="F236" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H236" t="str">
         <f t="shared" si="9"/>
@@ -10249,7 +10249,7 @@
         <v>251</v>
       </c>
       <c r="F237" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H237" t="str">
         <f t="shared" si="9"/>
@@ -10272,7 +10272,7 @@
         <v>256</v>
       </c>
       <c r="C238" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D238" t="s">
         <v>21</v>
@@ -10281,7 +10281,7 @@
         <v>251</v>
       </c>
       <c r="F238" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H238" t="str">
         <f t="shared" si="9"/>
@@ -10313,7 +10313,7 @@
         <v>251</v>
       </c>
       <c r="F239" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H239" t="str">
         <f t="shared" si="9"/>
@@ -10345,7 +10345,7 @@
         <v>251</v>
       </c>
       <c r="F240" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H240" t="str">
         <f t="shared" si="9"/>
@@ -10368,7 +10368,7 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D241" t="s">
         <v>21</v>
@@ -10377,7 +10377,7 @@
         <v>251</v>
       </c>
       <c r="F241" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H241" t="str">
         <f t="shared" si="9"/>
@@ -10400,7 +10400,7 @@
         <v>260</v>
       </c>
       <c r="C242" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D242" t="s">
         <v>21</v>
@@ -10409,7 +10409,7 @@
         <v>251</v>
       </c>
       <c r="F242" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H242" t="str">
         <f t="shared" si="9"/>
@@ -10432,7 +10432,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D243" t="s">
         <v>26</v>
@@ -10441,7 +10441,7 @@
         <v>251</v>
       </c>
       <c r="F243" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H243" t="str">
         <f t="shared" si="9"/>
@@ -10464,7 +10464,7 @@
         <v>262</v>
       </c>
       <c r="C244" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D244" t="s">
         <v>26</v>
@@ -10473,7 +10473,7 @@
         <v>251</v>
       </c>
       <c r="F244" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H244" t="str">
         <f t="shared" si="9"/>
@@ -10496,7 +10496,7 @@
         <v>263</v>
       </c>
       <c r="C245" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D245" t="s">
         <v>26</v>
@@ -10505,7 +10505,7 @@
         <v>251</v>
       </c>
       <c r="F245" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H245" t="str">
         <f t="shared" si="9"/>
@@ -10528,7 +10528,7 @@
         <v>264</v>
       </c>
       <c r="C246" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D246" t="s">
         <v>26</v>
@@ -10537,7 +10537,7 @@
         <v>251</v>
       </c>
       <c r="F246" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H246" t="str">
         <f t="shared" si="9"/>
@@ -10569,7 +10569,7 @@
         <v>251</v>
       </c>
       <c r="F247" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H247" t="str">
         <f t="shared" si="9"/>
@@ -10592,7 +10592,7 @@
         <v>266</v>
       </c>
       <c r="C248" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D248" t="s">
         <v>26</v>
@@ -10601,7 +10601,7 @@
         <v>251</v>
       </c>
       <c r="F248" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H248" t="str">
         <f t="shared" si="9"/>
@@ -10624,7 +10624,7 @@
         <v>267</v>
       </c>
       <c r="C249" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D249" t="s">
         <v>26</v>
@@ -10633,7 +10633,7 @@
         <v>251</v>
       </c>
       <c r="F249" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H249" t="str">
         <f t="shared" si="9"/>
@@ -10665,7 +10665,7 @@
         <v>251</v>
       </c>
       <c r="F250" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H250" t="str">
         <f t="shared" si="9"/>
@@ -10688,7 +10688,7 @@
         <v>269</v>
       </c>
       <c r="C251" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D251" t="s">
         <v>26</v>
@@ -10697,7 +10697,7 @@
         <v>251</v>
       </c>
       <c r="F251" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H251" t="str">
         <f t="shared" si="9"/>
@@ -10720,7 +10720,7 @@
         <v>270</v>
       </c>
       <c r="C252" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -10729,7 +10729,7 @@
         <v>276</v>
       </c>
       <c r="F252" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H252" t="str">
         <f t="shared" si="9"/>
@@ -10752,7 +10752,7 @@
         <v>271</v>
       </c>
       <c r="C253" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -10761,7 +10761,7 @@
         <v>276</v>
       </c>
       <c r="F253" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H253" t="str">
         <f t="shared" si="9"/>
@@ -10793,7 +10793,7 @@
         <v>276</v>
       </c>
       <c r="F254" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H254" t="str">
         <f t="shared" si="9"/>
@@ -10816,7 +10816,7 @@
         <v>273</v>
       </c>
       <c r="C255" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -10825,7 +10825,7 @@
         <v>276</v>
       </c>
       <c r="F255" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H255" t="str">
         <f t="shared" si="9"/>
@@ -10848,7 +10848,7 @@
         <v>274</v>
       </c>
       <c r="C256" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -10857,7 +10857,7 @@
         <v>276</v>
       </c>
       <c r="F256" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H256" t="str">
         <f t="shared" si="9"/>
@@ -10892,7 +10892,7 @@
         <v>276</v>
       </c>
       <c r="F257" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H257" t="str">
         <f t="shared" si="9"/>
@@ -10924,7 +10924,7 @@
         <v>276</v>
       </c>
       <c r="F258" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H258" t="str">
         <f t="shared" si="9"/>
@@ -10947,7 +10947,7 @@
         <v>278</v>
       </c>
       <c r="C259" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D259" t="s">
         <v>21</v>
@@ -10956,7 +10956,7 @@
         <v>276</v>
       </c>
       <c r="F259" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H259" t="str">
         <f t="shared" ref="H259:H297" si="12">IF(J259=1,L259&amp;".png","")</f>
@@ -10979,7 +10979,7 @@
         <v>279</v>
       </c>
       <c r="C260" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D260" t="s">
         <v>21</v>
@@ -10988,7 +10988,7 @@
         <v>276</v>
       </c>
       <c r="F260" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H260" t="str">
         <f t="shared" si="12"/>
@@ -11011,7 +11011,7 @@
         <v>280</v>
       </c>
       <c r="C261" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D261" t="s">
         <v>21</v>
@@ -11020,7 +11020,7 @@
         <v>276</v>
       </c>
       <c r="F261" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H261" t="str">
         <f t="shared" si="12"/>
@@ -11043,7 +11043,7 @@
         <v>281</v>
       </c>
       <c r="C262" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D262" t="s">
         <v>21</v>
@@ -11052,7 +11052,7 @@
         <v>276</v>
       </c>
       <c r="F262" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H262" t="str">
         <f t="shared" si="12"/>
@@ -11084,7 +11084,7 @@
         <v>276</v>
       </c>
       <c r="F263" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H263" t="str">
         <f t="shared" si="12"/>
@@ -11107,7 +11107,7 @@
         <v>283</v>
       </c>
       <c r="C264" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D264" t="s">
         <v>21</v>
@@ -11116,7 +11116,7 @@
         <v>276</v>
       </c>
       <c r="F264" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H264" t="str">
         <f t="shared" si="12"/>
@@ -11139,7 +11139,7 @@
         <v>284</v>
       </c>
       <c r="C265" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D265" t="s">
         <v>21</v>
@@ -11148,7 +11148,7 @@
         <v>276</v>
       </c>
       <c r="F265" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H265" t="str">
         <f t="shared" si="12"/>
@@ -11171,7 +11171,7 @@
         <v>285</v>
       </c>
       <c r="C266" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D266" t="s">
         <v>21</v>
@@ -11180,7 +11180,7 @@
         <v>276</v>
       </c>
       <c r="F266" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H266" t="str">
         <f t="shared" si="12"/>
@@ -11203,7 +11203,7 @@
         <v>286</v>
       </c>
       <c r="C267" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D267" t="s">
         <v>21</v>
@@ -11212,7 +11212,7 @@
         <v>276</v>
       </c>
       <c r="F267" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H267" t="str">
         <f t="shared" si="12"/>
@@ -11235,7 +11235,7 @@
         <v>287</v>
       </c>
       <c r="C268" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D268" t="s">
         <v>21</v>
@@ -11244,7 +11244,7 @@
         <v>276</v>
       </c>
       <c r="F268" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H268" t="str">
         <f t="shared" si="12"/>
@@ -11276,7 +11276,7 @@
         <v>276</v>
       </c>
       <c r="F269" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H269" t="str">
         <f t="shared" si="12"/>
@@ -11299,7 +11299,7 @@
         <v>289</v>
       </c>
       <c r="C270" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D270" t="s">
         <v>26</v>
@@ -11308,7 +11308,7 @@
         <v>276</v>
       </c>
       <c r="F270" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H270" t="str">
         <f t="shared" si="12"/>
@@ -11331,7 +11331,7 @@
         <v>290</v>
       </c>
       <c r="C271" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D271" t="s">
         <v>26</v>
@@ -11340,7 +11340,7 @@
         <v>276</v>
       </c>
       <c r="F271" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H271" t="str">
         <f t="shared" si="12"/>
@@ -11363,7 +11363,7 @@
         <v>291</v>
       </c>
       <c r="C272" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D272" t="s">
         <v>26</v>
@@ -11372,7 +11372,7 @@
         <v>276</v>
       </c>
       <c r="F272" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H272" t="str">
         <f t="shared" si="12"/>
@@ -11395,7 +11395,7 @@
         <v>292</v>
       </c>
       <c r="C273" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D273" t="s">
         <v>26</v>
@@ -11404,7 +11404,7 @@
         <v>276</v>
       </c>
       <c r="F273" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H273" t="str">
         <f t="shared" si="12"/>
@@ -11427,7 +11427,7 @@
         <v>293</v>
       </c>
       <c r="C274" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D274" t="s">
         <v>26</v>
@@ -11436,7 +11436,7 @@
         <v>276</v>
       </c>
       <c r="F274" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H274" t="str">
         <f t="shared" si="12"/>
@@ -11459,7 +11459,7 @@
         <v>294</v>
       </c>
       <c r="C275" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D275" t="s">
         <v>26</v>
@@ -11468,7 +11468,7 @@
         <v>276</v>
       </c>
       <c r="F275" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H275" t="str">
         <f t="shared" si="12"/>
@@ -11500,7 +11500,7 @@
         <v>276</v>
       </c>
       <c r="F276" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H276" t="str">
         <f t="shared" si="12"/>
@@ -11523,7 +11523,7 @@
         <v>296</v>
       </c>
       <c r="C277" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D277" t="s">
         <v>26</v>
@@ -11532,7 +11532,7 @@
         <v>276</v>
       </c>
       <c r="F277" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H277" t="str">
         <f t="shared" si="12"/>
@@ -11564,7 +11564,7 @@
         <v>276</v>
       </c>
       <c r="F278" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H278" t="str">
         <f t="shared" si="12"/>
@@ -11587,7 +11587,7 @@
         <v>298</v>
       </c>
       <c r="C279" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D279" t="s">
         <v>26</v>
@@ -11596,7 +11596,7 @@
         <v>276</v>
       </c>
       <c r="F279" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H279" t="str">
         <f t="shared" si="12"/>
@@ -11619,7 +11619,7 @@
         <v>299</v>
       </c>
       <c r="C280" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D280" t="s">
         <v>26</v>
@@ -11628,7 +11628,7 @@
         <v>276</v>
       </c>
       <c r="F280" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H280" t="str">
         <f t="shared" si="12"/>
@@ -11651,7 +11651,7 @@
         <v>300</v>
       </c>
       <c r="C281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -11660,7 +11660,7 @@
         <v>311</v>
       </c>
       <c r="F281" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H281" t="str">
         <f t="shared" si="12"/>
@@ -11683,7 +11683,7 @@
         <v>301</v>
       </c>
       <c r="C282" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -11692,7 +11692,7 @@
         <v>311</v>
       </c>
       <c r="F282" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H282" t="str">
         <f t="shared" si="12"/>
@@ -11715,7 +11715,7 @@
         <v>302</v>
       </c>
       <c r="C283" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D283" t="s">
         <v>21</v>
@@ -11724,7 +11724,7 @@
         <v>311</v>
       </c>
       <c r="F283" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H283" t="str">
         <f t="shared" si="12"/>
@@ -11747,7 +11747,7 @@
         <v>303</v>
       </c>
       <c r="C284" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D284" t="s">
         <v>21</v>
@@ -11756,7 +11756,7 @@
         <v>311</v>
       </c>
       <c r="F284" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H284" t="str">
         <f t="shared" si="12"/>
@@ -11779,7 +11779,7 @@
         <v>304</v>
       </c>
       <c r="C285" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D285" t="s">
         <v>21</v>
@@ -11788,7 +11788,7 @@
         <v>311</v>
       </c>
       <c r="F285" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H285" t="str">
         <f t="shared" si="12"/>
@@ -11811,7 +11811,7 @@
         <v>305</v>
       </c>
       <c r="C286" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D286" t="s">
         <v>26</v>
@@ -11820,7 +11820,7 @@
         <v>311</v>
       </c>
       <c r="F286" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H286" t="str">
         <f t="shared" si="12"/>
@@ -11843,7 +11843,7 @@
         <v>306</v>
       </c>
       <c r="C287" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D287" t="s">
         <v>26</v>
@@ -11852,7 +11852,7 @@
         <v>311</v>
       </c>
       <c r="F287" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H287" t="str">
         <f t="shared" si="12"/>
@@ -11875,7 +11875,7 @@
         <v>307</v>
       </c>
       <c r="C288" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D288" t="s">
         <v>26</v>
@@ -11884,7 +11884,7 @@
         <v>311</v>
       </c>
       <c r="F288" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H288" t="str">
         <f t="shared" si="12"/>
@@ -11916,7 +11916,7 @@
         <v>311</v>
       </c>
       <c r="F289" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H289" t="str">
         <f t="shared" si="12"/>
@@ -11939,7 +11939,7 @@
         <v>309</v>
       </c>
       <c r="C290" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D290" t="s">
         <v>26</v>
@@ -11948,7 +11948,7 @@
         <v>311</v>
       </c>
       <c r="F290" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H290" t="str">
         <f t="shared" si="12"/>
@@ -11971,7 +11971,7 @@
         <v>310</v>
       </c>
       <c r="C291" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D291" t="s">
         <v>26</v>
@@ -11980,7 +11980,7 @@
         <v>311</v>
       </c>
       <c r="F291" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H291" t="str">
         <f t="shared" si="12"/>
@@ -12012,7 +12012,7 @@
         <v>90</v>
       </c>
       <c r="F292" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H292" t="str">
         <f t="shared" si="12"/>
@@ -12044,7 +12044,7 @@
         <v>311</v>
       </c>
       <c r="F293" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H293" t="str">
         <f t="shared" si="12"/>
@@ -12064,7 +12064,7 @@
         <v>294</v>
       </c>
       <c r="B294" t="s">
-        <v>317</v>
+        <v>632</v>
       </c>
       <c r="C294" t="s">
         <v>315</v>
@@ -12076,7 +12076,7 @@
         <v>311</v>
       </c>
       <c r="F294" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H294" t="str">
         <f t="shared" si="12"/>
@@ -12096,10 +12096,10 @@
         <v>295</v>
       </c>
       <c r="B295" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C295" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D295" t="s">
         <v>21</v>
@@ -12108,7 +12108,7 @@
         <v>311</v>
       </c>
       <c r="F295" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H295" t="str">
         <f t="shared" si="12"/>
@@ -12128,10 +12128,10 @@
         <v>296</v>
       </c>
       <c r="B296" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C296" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D296" t="s">
         <v>26</v>
@@ -12140,7 +12140,7 @@
         <v>222</v>
       </c>
       <c r="F296" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H296" t="str">
         <f t="shared" si="12"/>
@@ -12160,19 +12160,19 @@
         <v>297</v>
       </c>
       <c r="B297" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C297" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D297" t="s">
         <v>26</v>
       </c>
       <c r="E297" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="F297" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H297" t="str">
         <f t="shared" si="12"/>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353D880D-7B2F-41EF-8E60-F4D904BE294B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06820BA-3B6D-4F93-80CF-A9222DBE2E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2943,7 +2943,10 @@
       </c>
       <c r="I9" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1008.mp4</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
       </c>
       <c r="L9">
         <f t="shared" si="2"/>
@@ -7115,7 +7118,10 @@
       </c>
       <c r="I139" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1138.mp4</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
       </c>
       <c r="L139">
         <f t="shared" si="8"/>
@@ -7278,7 +7284,10 @@
       </c>
       <c r="I144" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1143.mp4</v>
+      </c>
+      <c r="K144">
+        <v>1</v>
       </c>
       <c r="L144">
         <f t="shared" si="8"/>
@@ -7406,7 +7415,10 @@
       </c>
       <c r="I148" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1147.mp4</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
       </c>
       <c r="L148">
         <f t="shared" si="8"/>
@@ -7502,7 +7514,10 @@
       </c>
       <c r="I151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1150.mp4</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
       </c>
       <c r="L151">
         <f t="shared" si="8"/>
@@ -7994,7 +8009,10 @@
       </c>
       <c r="I166" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1165.mp4</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
       </c>
       <c r="L166">
         <f t="shared" si="8"/>
@@ -8186,7 +8204,10 @@
       </c>
       <c r="I172" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1171.mp4</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
       </c>
       <c r="L172">
         <f t="shared" si="8"/>
@@ -8640,7 +8661,10 @@
       </c>
       <c r="I186" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1185.mp4</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
       </c>
       <c r="L186">
         <f t="shared" si="8"/>
@@ -8896,7 +8920,10 @@
       </c>
       <c r="I194" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1193.mp4</v>
+      </c>
+      <c r="K194">
+        <v>1</v>
       </c>
       <c r="L194">
         <f t="shared" si="8"/>
@@ -9059,7 +9086,10 @@
       </c>
       <c r="I199" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1198.mp4</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
       </c>
       <c r="L199">
         <f t="shared" si="11"/>
@@ -9257,7 +9287,10 @@
       </c>
       <c r="I205" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1204.mp4</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
       </c>
       <c r="L205">
         <f t="shared" si="11"/>
@@ -9484,7 +9517,10 @@
       </c>
       <c r="I212" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1211.mp4</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
       </c>
       <c r="L212">
         <f t="shared" si="11"/>
@@ -9612,7 +9648,10 @@
       </c>
       <c r="I216" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1215.mp4</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
       </c>
       <c r="L216">
         <f t="shared" si="11"/>
@@ -9740,7 +9779,10 @@
       </c>
       <c r="I220" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1219.mp4</v>
+      </c>
+      <c r="K220">
+        <v>1</v>
       </c>
       <c r="L220">
         <f t="shared" si="11"/>
@@ -9836,7 +9878,10 @@
       </c>
       <c r="I223" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1222.mp4</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
       </c>
       <c r="L223">
         <f t="shared" si="11"/>
@@ -10156,7 +10201,10 @@
       </c>
       <c r="I233" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1233.mp4</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
       </c>
       <c r="L233">
         <f t="shared" si="11"/>
@@ -10284,7 +10332,10 @@
       </c>
       <c r="I237" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1237.mp4</v>
+      </c>
+      <c r="K237">
+        <v>1</v>
       </c>
       <c r="L237">
         <f t="shared" si="11"/>
@@ -10610,7 +10661,10 @@
       </c>
       <c r="I247" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1247.mp4</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
       </c>
       <c r="L247">
         <f t="shared" si="11"/>
@@ -10965,7 +11019,10 @@
       </c>
       <c r="I258" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1258.mp4</v>
+      </c>
+      <c r="K258">
+        <v>1</v>
       </c>
       <c r="L258">
         <f t="shared" si="11"/>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06820BA-3B6D-4F93-80CF-A9222DBE2E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D279A110-B47B-42D2-A3E6-D414A1F70634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -7942,7 +7942,10 @@
       </c>
       <c r="I164" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1163.mp4</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
       </c>
       <c r="L164">
         <f t="shared" si="8"/>
@@ -8076,7 +8079,10 @@
       </c>
       <c r="I168" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1167.mp4</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
       </c>
       <c r="L168">
         <f t="shared" si="8"/>
@@ -8172,7 +8178,10 @@
       </c>
       <c r="I171" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1170.mp4</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
       </c>
       <c r="L171">
         <f t="shared" si="8"/>
@@ -8530,7 +8539,10 @@
       </c>
       <c r="I182" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1181.mp4</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
       </c>
       <c r="L182">
         <f t="shared" si="8"/>
@@ -9453,7 +9465,10 @@
       </c>
       <c r="I210" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1209.mp4</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
       </c>
       <c r="L210">
         <f t="shared" si="11"/>
@@ -9846,7 +9861,10 @@
       </c>
       <c r="I222" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1221.mp4</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
       </c>
       <c r="L222">
         <f t="shared" si="11"/>
@@ -10300,7 +10318,10 @@
       </c>
       <c r="I236" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1236.mp4</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
       </c>
       <c r="L236">
         <f t="shared" si="11"/>
@@ -10696,7 +10717,10 @@
       </c>
       <c r="I248" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1248.mp4</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
       </c>
       <c r="L248">
         <f t="shared" si="11"/>
@@ -10824,7 +10848,10 @@
       </c>
       <c r="I252" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1252.mp4</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
       </c>
       <c r="L252">
         <f t="shared" si="11"/>
@@ -11537,7 +11564,10 @@
       </c>
       <c r="I274" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1274.mp4</v>
+      </c>
+      <c r="K274">
+        <v>1</v>
       </c>
       <c r="L274">
         <f t="shared" si="14"/>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D279A110-B47B-42D2-A3E6-D414A1F70634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706DE5F7-663E-443C-A9C3-F7276CD3CF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -8507,7 +8507,10 @@
       </c>
       <c r="I181" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1180.mp4</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
       </c>
       <c r="L181">
         <f t="shared" si="8"/>
@@ -8539,10 +8542,7 @@
       </c>
       <c r="I182" t="str">
         <f t="shared" si="7"/>
-        <v>1181.mp4</v>
-      </c>
-      <c r="K182">
-        <v>1</v>
+        <v/>
       </c>
       <c r="L182">
         <f t="shared" si="8"/>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05377B76-88A6-42BD-B9CD-DAFF3B4B1CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB313DF-D403-4570-A4FC-0833A80CA83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="641">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2281,6 +2281,26 @@
   </si>
   <si>
     <t>깨모다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2티어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>killgusdnk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2648,7 +2668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A2A291-B3BF-4EBE-93A6-386812DCA76D}">
-  <dimension ref="A1:L299"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="2" max="2" width="10.9375" bestFit="1" customWidth="1"/>
@@ -3746,7 +3766,10 @@
       </c>
       <c r="I33" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1031.mp4</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
       </c>
       <c r="L33">
         <f t="shared" si="2"/>
@@ -4043,9 +4066,12 @@
       </c>
       <c r="I42" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1039.mp4</v>
       </c>
       <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
         <v>1</v>
       </c>
       <c r="L42">
@@ -4244,9 +4270,12 @@
       </c>
       <c r="I48" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1045.mp4</v>
       </c>
       <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
         <v>1</v>
       </c>
       <c r="L48">
@@ -4637,9 +4666,12 @@
       </c>
       <c r="I60" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1057.mp4</v>
       </c>
       <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
         <v>1</v>
       </c>
       <c r="L60">
@@ -6240,7 +6272,10 @@
       </c>
       <c r="I110" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1107.mp4</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
       </c>
       <c r="L110">
         <f t="shared" si="11"/>
@@ -7104,7 +7139,10 @@
       </c>
       <c r="I137" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1134.mp4</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
       </c>
       <c r="L137">
         <f t="shared" si="14"/>
@@ -7168,7 +7206,10 @@
       </c>
       <c r="I139" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1136.mp4</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
       </c>
       <c r="L139">
         <f t="shared" si="14"/>
@@ -7861,7 +7902,10 @@
       </c>
       <c r="I160" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1157.mp4</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
       </c>
       <c r="L160">
         <f t="shared" si="14"/>
@@ -11190,15 +11234,15 @@
         <v>588</v>
       </c>
       <c r="H261" t="str">
-        <f t="shared" ref="H261:H299" si="18">IF(J261=1,L261&amp;".png","")</f>
+        <f t="shared" ref="H261:H300" si="18">IF(J261=1,L261&amp;".png","")</f>
         <v/>
       </c>
       <c r="I261" t="str">
-        <f t="shared" ref="I261:I299" si="19">IF(K261=1,L261&amp;".mp4","")</f>
+        <f t="shared" ref="I261:I300" si="19">IF(K261=1,L261&amp;".mp4","")</f>
         <v/>
       </c>
       <c r="L261">
-        <f t="shared" ref="L261:L299" si="20">1000+A261</f>
+        <f t="shared" ref="L261:L301" si="20">1000+A261</f>
         <v>1259</v>
       </c>
     </row>
@@ -12425,6 +12469,41 @@
       <c r="L299">
         <f t="shared" si="20"/>
         <v>1297</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300" t="s">
+        <v>636</v>
+      </c>
+      <c r="C300" t="s">
+        <v>637</v>
+      </c>
+      <c r="D300" t="s">
+        <v>638</v>
+      </c>
+      <c r="E300" t="s">
+        <v>639</v>
+      </c>
+      <c r="F300" t="s">
+        <v>640</v>
+      </c>
+      <c r="H300" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="I300" t="str">
+        <f t="shared" si="19"/>
+        <v>1298.mp4</v>
+      </c>
+      <c r="K300">
+        <v>1</v>
+      </c>
+      <c r="L300">
+        <f t="shared" si="20"/>
+        <v>1298</v>
       </c>
     </row>
   </sheetData>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB313DF-D403-4570-A4FC-0833A80CA83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E906974-4FAE-4DC1-A5EF-FF1344D3AA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -9888,7 +9888,10 @@
       </c>
       <c r="I220" t="str">
         <f t="shared" si="16"/>
-        <v/>
+        <v>1217.mp4</v>
+      </c>
+      <c r="K220">
+        <v>1</v>
       </c>
       <c r="L220">
         <f t="shared" si="17"/>
@@ -11242,7 +11245,7 @@
         <v/>
       </c>
       <c r="L261">
-        <f t="shared" ref="L261:L301" si="20">1000+A261</f>
+        <f t="shared" ref="L261:L300" si="20">1000+A261</f>
         <v>1259</v>
       </c>
     </row>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E906974-4FAE-4DC1-A5EF-FF1344D3AA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BDC6FB-C1E7-43B0-B6D4-03EBFD55978E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -9856,7 +9856,10 @@
       </c>
       <c r="I219" t="str">
         <f t="shared" si="16"/>
-        <v/>
+        <v>1216.mp4</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
       </c>
       <c r="L219">
         <f t="shared" si="17"/>
@@ -9923,7 +9926,10 @@
       </c>
       <c r="I221" t="str">
         <f t="shared" si="16"/>
-        <v/>
+        <v>1218.mp4</v>
+      </c>
+      <c r="K221">
+        <v>1</v>
       </c>
       <c r="L221">
         <f t="shared" si="17"/>
@@ -9990,7 +9996,10 @@
       </c>
       <c r="I223" t="str">
         <f t="shared" si="16"/>
-        <v/>
+        <v>1220.mp4</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
       </c>
       <c r="L223">
         <f t="shared" si="17"/>
@@ -12435,7 +12444,10 @@
       </c>
       <c r="I298" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>1296.mp4</v>
+      </c>
+      <c r="K298">
+        <v>1</v>
       </c>
       <c r="L298">
         <f t="shared" si="20"/>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BDC6FB-C1E7-43B0-B6D4-03EBFD55978E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3583DF3F-68CC-497E-894F-1291128299E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="673">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1012,10 +1012,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>경콩이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>밥새</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1192,10 +1188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>혜요이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>진땅콩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2301,6 +2293,368 @@
   </si>
   <si>
     <t>killgusdnk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gks2wl</t>
+  </si>
+  <si>
+    <t>앵지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라히</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1티어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khc2566</t>
+  </si>
+  <si>
+    <t>헤요이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대학명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캄몬스타즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑카데미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨나인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엠비대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와플대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴캣슬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>👾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>캄몬스타즈</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🧑🏿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>흑카데미</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🐦‍🔥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>JSA</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⭐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>케이대</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>9️⃣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>씨나인</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🐯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>엠비대</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🧇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>와플대</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>👨🏻‍⚕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수술대</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🐈️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>뉴캣슬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🏜️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HM</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BGM</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DM</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경콩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2308,7 +2662,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2323,6 +2677,18 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2347,11 +2713,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2668,7 +3037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A2A291-B3BF-4EBE-93A6-386812DCA76D}">
-  <dimension ref="A1:L300"/>
+  <dimension ref="A1:Q302"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="2" max="2" width="10.9375" bestFit="1" customWidth="1"/>
@@ -2681,7 +3050,7 @@
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2701,25 +3070,31 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>624</v>
+      </c>
+      <c r="H1" t="s">
+        <v>625</v>
+      </c>
+      <c r="I1" t="s">
         <v>626</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>627</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>628</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>629</v>
       </c>
-      <c r="K1" t="s">
-        <v>630</v>
-      </c>
-      <c r="L1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O1" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2727,7 +3102,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -2736,7 +3111,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G2" s="1">
         <v>46167</v>
@@ -2753,8 +3128,14 @@
         <f>1000+A2</f>
         <v>1001</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O2" t="s">
+        <v>648</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2771,7 +3152,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" ref="H3:H68" si="0">IF(J3=1,L3&amp;".png","")</f>
@@ -2785,8 +3166,14 @@
         <f t="shared" ref="L3:L68" si="2">1000+A3</f>
         <v>1002</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O3" t="s">
+        <v>649</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2803,7 +3190,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
@@ -2817,8 +3204,14 @@
         <f t="shared" si="2"/>
         <v>1003</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O4" t="s">
+        <v>650</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2826,7 +3219,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -2835,7 +3228,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
@@ -2849,8 +3242,14 @@
         <f t="shared" si="2"/>
         <v>1004</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O5" t="s">
+        <v>651</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2858,7 +3257,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -2867,7 +3266,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
@@ -2884,8 +3283,14 @@
         <f t="shared" si="2"/>
         <v>1005</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O6" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2902,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
@@ -2916,8 +3321,14 @@
         <f t="shared" si="2"/>
         <v>1006</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O7" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2925,7 +3336,7 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -2934,7 +3345,7 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="0"/>
@@ -2948,8 +3359,14 @@
         <f t="shared" si="2"/>
         <v>1007</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O8" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2957,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -2966,7 +3383,7 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" si="0"/>
@@ -2983,16 +3400,22 @@
         <f t="shared" si="2"/>
         <v>1008</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O9" t="s">
+        <v>655</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -3001,7 +3424,7 @@
         <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H10" t="str">
         <f t="shared" ref="H10" si="3">IF(J10=1,L10&amp;".png","")</f>
@@ -3018,8 +3441,14 @@
         <f t="shared" ref="L10" si="5">1000+A10</f>
         <v>1008</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O10" t="s">
+        <v>656</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3027,7 +3456,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -3036,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="0"/>
@@ -3050,8 +3479,14 @@
         <f t="shared" si="2"/>
         <v>1009</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O11" t="s">
+        <v>657</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3059,7 +3494,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
@@ -3068,7 +3503,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" si="0"/>
@@ -3082,8 +3517,14 @@
         <f t="shared" si="2"/>
         <v>1010</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O12" t="s">
+        <v>658</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3100,7 +3541,7 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="0"/>
@@ -3114,8 +3555,14 @@
         <f t="shared" si="2"/>
         <v>1011</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="O13" t="s">
+        <v>659</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3132,7 +3579,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H14" t="str">
         <f t="shared" si="0"/>
@@ -3147,7 +3594,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3155,7 +3602,7 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -3164,7 +3611,7 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H15" t="str">
         <f t="shared" si="0"/>
@@ -3182,7 +3629,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3190,7 +3637,7 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
@@ -3199,7 +3646,7 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H16" t="str">
         <f t="shared" si="0"/>
@@ -3234,7 +3681,7 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H17" t="str">
         <f t="shared" si="0"/>
@@ -3266,7 +3713,7 @@
         <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H18" t="str">
         <f t="shared" si="0"/>
@@ -3298,7 +3745,7 @@
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="0"/>
@@ -3330,7 +3777,7 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H20" t="str">
         <f t="shared" si="0"/>
@@ -3353,7 +3800,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -3362,7 +3809,7 @@
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H21" t="str">
         <f t="shared" si="0"/>
@@ -3397,7 +3844,7 @@
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H22" t="str">
         <f t="shared" si="0"/>
@@ -3420,7 +3867,7 @@
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -3429,7 +3876,7 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H23" t="str">
         <f t="shared" si="0"/>
@@ -3452,7 +3899,7 @@
         <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -3461,7 +3908,7 @@
         <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H24" t="str">
         <f t="shared" si="0"/>
@@ -3487,7 +3934,7 @@
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -3496,7 +3943,7 @@
         <v>27</v>
       </c>
       <c r="F25" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="0"/>
@@ -3522,7 +3969,7 @@
         <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -3531,7 +3978,7 @@
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H26" t="str">
         <f t="shared" si="0"/>
@@ -3563,7 +4010,7 @@
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H27" t="str">
         <f t="shared" si="0"/>
@@ -3595,7 +4042,7 @@
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H28" t="str">
         <f t="shared" si="0"/>
@@ -3618,7 +4065,7 @@
         <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D29" t="s">
         <v>21</v>
@@ -3627,7 +4074,7 @@
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H29" t="str">
         <f t="shared" si="0"/>
@@ -3662,7 +4109,7 @@
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H30" t="str">
         <f t="shared" si="0"/>
@@ -3694,7 +4141,7 @@
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="0"/>
@@ -3717,7 +4164,7 @@
         <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D32" t="s">
         <v>21</v>
@@ -3726,7 +4173,7 @@
         <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H32" t="str">
         <f t="shared" si="0"/>
@@ -3749,7 +4196,7 @@
         <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D33" t="s">
         <v>21</v>
@@ -3758,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H33" t="str">
         <f t="shared" si="0"/>
@@ -3784,7 +4231,7 @@
         <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
@@ -3793,7 +4240,7 @@
         <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H34" t="str">
         <f t="shared" si="0"/>
@@ -3816,7 +4263,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D35" t="s">
         <v>21</v>
@@ -3825,7 +4272,7 @@
         <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H35" t="str">
         <f t="shared" si="0"/>
@@ -3848,7 +4295,7 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D36" t="s">
         <v>21</v>
@@ -3857,7 +4304,7 @@
         <v>27</v>
       </c>
       <c r="F36" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="0"/>
@@ -3880,10 +4327,10 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C37" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D37" t="s">
         <v>21</v>
@@ -3892,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H37" t="str">
         <f t="shared" ref="H37" si="6">IF(J37=1,L37&amp;".png","")</f>
@@ -3918,7 +4365,7 @@
         <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D38" t="s">
         <v>26</v>
@@ -3927,7 +4374,7 @@
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H38" t="str">
         <f t="shared" si="0"/>
@@ -3959,7 +4406,7 @@
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" si="0"/>
@@ -3991,7 +4438,7 @@
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" si="0"/>
@@ -4014,7 +4461,7 @@
         <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>312</v>
+        <v>10</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -4023,7 +4470,7 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H41" t="str">
         <f t="shared" si="0"/>
@@ -4049,7 +4496,7 @@
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D42" t="s">
         <v>26</v>
@@ -4058,7 +4505,7 @@
         <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H42" t="str">
         <f t="shared" si="0"/>
@@ -4087,7 +4534,7 @@
         <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
@@ -4096,7 +4543,7 @@
         <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H43" t="str">
         <f t="shared" si="0"/>
@@ -4131,7 +4578,7 @@
         <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H44" t="str">
         <f t="shared" si="0"/>
@@ -4154,7 +4601,7 @@
         <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
@@ -4163,7 +4610,7 @@
         <v>27</v>
       </c>
       <c r="F45" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H45" t="str">
         <f t="shared" si="0"/>
@@ -4198,7 +4645,7 @@
         <v>62</v>
       </c>
       <c r="F46" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H46" t="str">
         <f t="shared" si="0"/>
@@ -4221,7 +4668,7 @@
         <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -4230,7 +4677,7 @@
         <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H47" t="str">
         <f t="shared" si="0"/>
@@ -4253,7 +4700,7 @@
         <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -4262,7 +4709,7 @@
         <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H48" t="str">
         <f t="shared" si="0"/>
@@ -4291,7 +4738,7 @@
         <v>57</v>
       </c>
       <c r="C49" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -4300,7 +4747,7 @@
         <v>62</v>
       </c>
       <c r="F49" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H49" t="str">
         <f t="shared" si="0"/>
@@ -4323,7 +4770,7 @@
         <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -4332,7 +4779,7 @@
         <v>62</v>
       </c>
       <c r="F50" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H50" t="str">
         <f t="shared" si="0"/>
@@ -4358,7 +4805,7 @@
         <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -4367,7 +4814,7 @@
         <v>62</v>
       </c>
       <c r="F51" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H51" t="str">
         <f t="shared" si="0"/>
@@ -4390,7 +4837,7 @@
         <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -4399,7 +4846,7 @@
         <v>62</v>
       </c>
       <c r="F52" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H52" t="str">
         <f t="shared" si="0"/>
@@ -4422,7 +4869,7 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -4431,7 +4878,7 @@
         <v>62</v>
       </c>
       <c r="F53" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H53" t="str">
         <f t="shared" si="0"/>
@@ -4454,7 +4901,7 @@
         <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D54" t="s">
         <v>21</v>
@@ -4463,7 +4910,7 @@
         <v>62</v>
       </c>
       <c r="F54" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H54" t="str">
         <f t="shared" si="0"/>
@@ -4489,7 +4936,7 @@
         <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D55" t="s">
         <v>21</v>
@@ -4498,7 +4945,7 @@
         <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H55" t="str">
         <f t="shared" si="0"/>
@@ -4530,7 +4977,7 @@
         <v>27</v>
       </c>
       <c r="F56" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H56" t="str">
         <f t="shared" si="0"/>
@@ -4553,7 +5000,7 @@
         <v>66</v>
       </c>
       <c r="C57" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D57" t="s">
         <v>21</v>
@@ -4562,7 +5009,7 @@
         <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H57" t="str">
         <f t="shared" si="0"/>
@@ -4585,7 +5032,7 @@
         <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D58" t="s">
         <v>21</v>
@@ -4594,7 +5041,7 @@
         <v>62</v>
       </c>
       <c r="F58" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H58" t="str">
         <f t="shared" si="0"/>
@@ -4617,7 +5064,7 @@
         <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>322</v>
       </c>
       <c r="D59" t="s">
         <v>21</v>
@@ -4626,7 +5073,7 @@
         <v>62</v>
       </c>
       <c r="F59" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H59" t="str">
         <f t="shared" si="0"/>
@@ -4649,7 +5096,7 @@
         <v>69</v>
       </c>
       <c r="C60" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D60" t="s">
         <v>21</v>
@@ -4658,7 +5105,7 @@
         <v>62</v>
       </c>
       <c r="F60" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H60" t="str">
         <f t="shared" si="0"/>
@@ -4687,7 +5134,7 @@
         <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D61" t="s">
         <v>21</v>
@@ -4696,7 +5143,7 @@
         <v>62</v>
       </c>
       <c r="F61" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H61" t="str">
         <f t="shared" si="0"/>
@@ -4728,7 +5175,7 @@
         <v>62</v>
       </c>
       <c r="F62" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H62" t="str">
         <f t="shared" si="0"/>
@@ -4760,7 +5207,7 @@
         <v>62</v>
       </c>
       <c r="F63" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H63" t="str">
         <f t="shared" si="0"/>
@@ -4783,7 +5230,7 @@
         <v>73</v>
       </c>
       <c r="C64" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D64" t="s">
         <v>21</v>
@@ -4792,7 +5239,7 @@
         <v>62</v>
       </c>
       <c r="F64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H64" t="str">
         <f t="shared" si="0"/>
@@ -4824,7 +5271,7 @@
         <v>62</v>
       </c>
       <c r="F65" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H65" t="str">
         <f t="shared" si="0"/>
@@ -4847,7 +5294,7 @@
         <v>75</v>
       </c>
       <c r="C66" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D66" t="s">
         <v>21</v>
@@ -4856,7 +5303,7 @@
         <v>62</v>
       </c>
       <c r="F66" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H66" t="str">
         <f t="shared" si="0"/>
@@ -4879,7 +5326,7 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D67" t="s">
         <v>21</v>
@@ -4888,7 +5335,7 @@
         <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H67" t="str">
         <f t="shared" si="0"/>
@@ -4920,7 +5367,7 @@
         <v>62</v>
       </c>
       <c r="F68" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H68" t="str">
         <f t="shared" si="0"/>
@@ -4952,7 +5399,7 @@
         <v>62</v>
       </c>
       <c r="F69" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H69" t="str">
         <f t="shared" ref="H69:H132" si="9">IF(J69=1,L69&amp;".png","")</f>
@@ -4975,7 +5422,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D70" t="s">
         <v>26</v>
@@ -4984,7 +5431,7 @@
         <v>62</v>
       </c>
       <c r="F70" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H70" t="str">
         <f t="shared" si="9"/>
@@ -5016,7 +5463,7 @@
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H71" t="str">
         <f t="shared" si="9"/>
@@ -5039,7 +5486,7 @@
         <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D72" t="s">
         <v>26</v>
@@ -5048,7 +5495,7 @@
         <v>62</v>
       </c>
       <c r="F72" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H72" t="str">
         <f t="shared" si="9"/>
@@ -5080,7 +5527,7 @@
         <v>62</v>
       </c>
       <c r="F73" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H73" t="str">
         <f t="shared" si="9"/>
@@ -5112,7 +5559,7 @@
         <v>62</v>
       </c>
       <c r="F74" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H74" t="str">
         <f t="shared" si="9"/>
@@ -5135,7 +5582,7 @@
         <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D75" t="s">
         <v>26</v>
@@ -5144,7 +5591,7 @@
         <v>62</v>
       </c>
       <c r="F75" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H75" t="str">
         <f t="shared" si="9"/>
@@ -5176,7 +5623,7 @@
         <v>62</v>
       </c>
       <c r="F76" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H76" t="str">
         <f t="shared" si="9"/>
@@ -5208,7 +5655,7 @@
         <v>62</v>
       </c>
       <c r="F77" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H77" t="str">
         <f t="shared" si="9"/>
@@ -5231,7 +5678,7 @@
         <v>87</v>
       </c>
       <c r="C78" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D78" t="s">
         <v>26</v>
@@ -5240,7 +5687,7 @@
         <v>62</v>
       </c>
       <c r="F78" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H78" t="str">
         <f t="shared" si="9"/>
@@ -5263,7 +5710,7 @@
         <v>88</v>
       </c>
       <c r="C79" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5272,7 +5719,7 @@
         <v>90</v>
       </c>
       <c r="F79" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H79" t="str">
         <f t="shared" si="9"/>
@@ -5304,7 +5751,7 @@
         <v>90</v>
       </c>
       <c r="F80" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H80" t="str">
         <f t="shared" si="9"/>
@@ -5327,7 +5774,7 @@
         <v>91</v>
       </c>
       <c r="C81" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5336,7 +5783,7 @@
         <v>90</v>
       </c>
       <c r="F81" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H81" t="str">
         <f t="shared" si="9"/>
@@ -5359,7 +5806,7 @@
         <v>92</v>
       </c>
       <c r="C82" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D82" t="s">
         <v>21</v>
@@ -5368,7 +5815,7 @@
         <v>90</v>
       </c>
       <c r="F82" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H82" t="str">
         <f t="shared" si="9"/>
@@ -5391,7 +5838,7 @@
         <v>93</v>
       </c>
       <c r="C83" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D83" t="s">
         <v>21</v>
@@ -5400,7 +5847,7 @@
         <v>90</v>
       </c>
       <c r="F83" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H83" t="str">
         <f t="shared" si="9"/>
@@ -5423,7 +5870,7 @@
         <v>94</v>
       </c>
       <c r="C84" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D84" t="s">
         <v>21</v>
@@ -5432,7 +5879,7 @@
         <v>90</v>
       </c>
       <c r="F84" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H84" t="str">
         <f t="shared" si="9"/>
@@ -5455,7 +5902,7 @@
         <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D85" t="s">
         <v>21</v>
@@ -5464,7 +5911,7 @@
         <v>90</v>
       </c>
       <c r="F85" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H85" t="str">
         <f t="shared" si="9"/>
@@ -5487,7 +5934,7 @@
         <v>96</v>
       </c>
       <c r="C86" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D86" t="s">
         <v>21</v>
@@ -5496,7 +5943,7 @@
         <v>90</v>
       </c>
       <c r="F86" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H86" t="str">
         <f t="shared" si="9"/>
@@ -5528,7 +5975,7 @@
         <v>90</v>
       </c>
       <c r="F87" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H87" t="str">
         <f t="shared" si="9"/>
@@ -5560,7 +6007,7 @@
         <v>90</v>
       </c>
       <c r="F88" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H88" t="str">
         <f t="shared" si="9"/>
@@ -5583,7 +6030,7 @@
         <v>99</v>
       </c>
       <c r="C89" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D89" t="s">
         <v>26</v>
@@ -5592,7 +6039,7 @@
         <v>90</v>
       </c>
       <c r="F89" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H89" t="str">
         <f t="shared" si="9"/>
@@ -5615,7 +6062,7 @@
         <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D90" t="s">
         <v>26</v>
@@ -5624,7 +6071,7 @@
         <v>90</v>
       </c>
       <c r="F90" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H90" t="str">
         <f t="shared" si="9"/>
@@ -5647,7 +6094,7 @@
         <v>101</v>
       </c>
       <c r="C91" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D91" t="s">
         <v>26</v>
@@ -5656,7 +6103,7 @@
         <v>90</v>
       </c>
       <c r="F91" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H91" t="str">
         <f t="shared" si="9"/>
@@ -5679,7 +6126,7 @@
         <v>102</v>
       </c>
       <c r="C92" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D92" t="s">
         <v>26</v>
@@ -5688,7 +6135,7 @@
         <v>90</v>
       </c>
       <c r="F92" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H92" t="str">
         <f t="shared" si="9"/>
@@ -5720,7 +6167,7 @@
         <v>90</v>
       </c>
       <c r="F93" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H93" t="str">
         <f t="shared" si="9"/>
@@ -5743,7 +6190,7 @@
         <v>104</v>
       </c>
       <c r="C94" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
@@ -5752,7 +6199,7 @@
         <v>90</v>
       </c>
       <c r="F94" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H94" t="str">
         <f t="shared" si="9"/>
@@ -5775,7 +6222,7 @@
         <v>105</v>
       </c>
       <c r="C95" t="s">
-        <v>327</v>
+        <v>10</v>
       </c>
       <c r="D95" t="s">
         <v>26</v>
@@ -5784,7 +6231,7 @@
         <v>90</v>
       </c>
       <c r="F95" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H95" t="str">
         <f t="shared" si="9"/>
@@ -5807,7 +6254,7 @@
         <v>106</v>
       </c>
       <c r="C96" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
@@ -5816,7 +6263,7 @@
         <v>90</v>
       </c>
       <c r="F96" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H96" t="str">
         <f t="shared" si="9"/>
@@ -5839,7 +6286,7 @@
         <v>107</v>
       </c>
       <c r="C97" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D97" t="s">
         <v>26</v>
@@ -5848,7 +6295,7 @@
         <v>90</v>
       </c>
       <c r="F97" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H97" t="str">
         <f t="shared" si="9"/>
@@ -5880,7 +6327,7 @@
         <v>90</v>
       </c>
       <c r="F98" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H98" t="str">
         <f t="shared" si="9"/>
@@ -5912,7 +6359,7 @@
         <v>90</v>
       </c>
       <c r="F99" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H99" t="str">
         <f t="shared" si="9"/>
@@ -5935,7 +6382,7 @@
         <v>111</v>
       </c>
       <c r="C100" t="s">
-        <v>10</v>
+        <v>325</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -5944,7 +6391,7 @@
         <v>110</v>
       </c>
       <c r="F100" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H100" t="str">
         <f t="shared" si="9"/>
@@ -5967,7 +6414,7 @@
         <v>112</v>
       </c>
       <c r="C101" t="s">
-        <v>327</v>
+        <v>10</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -5976,7 +6423,7 @@
         <v>110</v>
       </c>
       <c r="F101" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H101" t="str">
         <f t="shared" si="9"/>
@@ -5999,7 +6446,7 @@
         <v>113</v>
       </c>
       <c r="C102" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6008,7 +6455,7 @@
         <v>110</v>
       </c>
       <c r="F102" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H102" t="str">
         <f t="shared" si="9"/>
@@ -6031,7 +6478,7 @@
         <v>114</v>
       </c>
       <c r="C103" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6040,7 +6487,7 @@
         <v>110</v>
       </c>
       <c r="F103" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H103" t="str">
         <f t="shared" si="9"/>
@@ -6072,7 +6519,7 @@
         <v>110</v>
       </c>
       <c r="F104" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H104" t="str">
         <f t="shared" si="9"/>
@@ -6095,7 +6542,7 @@
         <v>116</v>
       </c>
       <c r="C105" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D105" t="s">
         <v>21</v>
@@ -6104,7 +6551,7 @@
         <v>110</v>
       </c>
       <c r="F105" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H105" t="str">
         <f t="shared" si="9"/>
@@ -6136,7 +6583,7 @@
         <v>110</v>
       </c>
       <c r="F106" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H106" t="str">
         <f t="shared" si="9"/>
@@ -6159,7 +6606,7 @@
         <v>117</v>
       </c>
       <c r="C107" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D107" t="s">
         <v>26</v>
@@ -6168,7 +6615,7 @@
         <v>110</v>
       </c>
       <c r="F107" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H107" t="str">
         <f t="shared" si="9"/>
@@ -6191,7 +6638,7 @@
         <v>118</v>
       </c>
       <c r="C108" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D108" t="s">
         <v>26</v>
@@ -6200,7 +6647,7 @@
         <v>110</v>
       </c>
       <c r="F108" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H108" t="str">
         <f t="shared" si="9"/>
@@ -6223,7 +6670,7 @@
         <v>119</v>
       </c>
       <c r="C109" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -6232,7 +6679,7 @@
         <v>110</v>
       </c>
       <c r="F109" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H109" t="str">
         <f t="shared" si="9"/>
@@ -6252,10 +6699,10 @@
         <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C110" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D110" t="s">
         <v>26</v>
@@ -6264,7 +6711,7 @@
         <v>110</v>
       </c>
       <c r="F110" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H110" t="str">
         <f t="shared" si="9"/>
@@ -6290,7 +6737,7 @@
         <v>120</v>
       </c>
       <c r="C111" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
@@ -6299,7 +6746,7 @@
         <v>110</v>
       </c>
       <c r="F111" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H111" t="str">
         <f t="shared" si="9"/>
@@ -6322,7 +6769,7 @@
         <v>121</v>
       </c>
       <c r="C112" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D112" t="s">
         <v>26</v>
@@ -6331,7 +6778,7 @@
         <v>110</v>
       </c>
       <c r="F112" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H112" t="str">
         <f t="shared" si="9"/>
@@ -6354,7 +6801,7 @@
         <v>122</v>
       </c>
       <c r="C113" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D113" t="s">
         <v>26</v>
@@ -6363,7 +6810,7 @@
         <v>110</v>
       </c>
       <c r="F113" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H113" t="str">
         <f t="shared" si="9"/>
@@ -6386,7 +6833,7 @@
         <v>123</v>
       </c>
       <c r="C114" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D114" t="s">
         <v>26</v>
@@ -6395,7 +6842,7 @@
         <v>110</v>
       </c>
       <c r="F114" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H114" t="str">
         <f t="shared" si="9"/>
@@ -6418,7 +6865,7 @@
         <v>124</v>
       </c>
       <c r="C115" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6427,7 +6874,7 @@
         <v>126</v>
       </c>
       <c r="F115" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H115" t="str">
         <f t="shared" si="9"/>
@@ -6450,7 +6897,7 @@
         <v>125</v>
       </c>
       <c r="C116" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6459,7 +6906,7 @@
         <v>126</v>
       </c>
       <c r="F116" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H116" t="str">
         <f t="shared" si="9"/>
@@ -6482,7 +6929,7 @@
         <v>127</v>
       </c>
       <c r="C117" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D117" t="s">
         <v>21</v>
@@ -6491,7 +6938,7 @@
         <v>126</v>
       </c>
       <c r="F117" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H117" t="str">
         <f t="shared" si="9"/>
@@ -6523,7 +6970,7 @@
         <v>126</v>
       </c>
       <c r="F118" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H118" t="str">
         <f t="shared" si="9"/>
@@ -6546,7 +6993,7 @@
         <v>129</v>
       </c>
       <c r="C119" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D119" t="s">
         <v>26</v>
@@ -6555,7 +7002,7 @@
         <v>126</v>
       </c>
       <c r="F119" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H119" t="str">
         <f t="shared" si="9"/>
@@ -6578,7 +7025,7 @@
         <v>130</v>
       </c>
       <c r="C120" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -6587,7 +7034,7 @@
         <v>126</v>
       </c>
       <c r="F120" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H120" t="str">
         <f t="shared" si="9"/>
@@ -6610,7 +7057,7 @@
         <v>131</v>
       </c>
       <c r="C121" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D121" t="s">
         <v>26</v>
@@ -6619,7 +7066,7 @@
         <v>126</v>
       </c>
       <c r="F121" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H121" t="str">
         <f t="shared" si="9"/>
@@ -6642,7 +7089,7 @@
         <v>132</v>
       </c>
       <c r="C122" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D122" t="s">
         <v>26</v>
@@ -6651,7 +7098,7 @@
         <v>126</v>
       </c>
       <c r="F122" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H122" t="str">
         <f t="shared" si="9"/>
@@ -6674,7 +7121,7 @@
         <v>133</v>
       </c>
       <c r="C123" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D123" t="s">
         <v>26</v>
@@ -6683,7 +7130,7 @@
         <v>126</v>
       </c>
       <c r="F123" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H123" t="str">
         <f t="shared" si="9"/>
@@ -6706,7 +7153,7 @@
         <v>134</v>
       </c>
       <c r="C124" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6715,7 +7162,7 @@
         <v>137</v>
       </c>
       <c r="F124" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H124" t="str">
         <f t="shared" si="9"/>
@@ -6738,7 +7185,7 @@
         <v>135</v>
       </c>
       <c r="C125" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6747,7 +7194,7 @@
         <v>137</v>
       </c>
       <c r="F125" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H125" t="str">
         <f t="shared" si="9"/>
@@ -6770,7 +7217,7 @@
         <v>136</v>
       </c>
       <c r="C126" t="s">
-        <v>328</v>
+        <v>10</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6779,7 +7226,7 @@
         <v>137</v>
       </c>
       <c r="F126" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H126" t="str">
         <f t="shared" si="9"/>
@@ -6802,7 +7249,7 @@
         <v>138</v>
       </c>
       <c r="C127" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D127" t="s">
         <v>26</v>
@@ -6811,7 +7258,7 @@
         <v>137</v>
       </c>
       <c r="F127" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H127" t="str">
         <f t="shared" si="9"/>
@@ -6834,7 +7281,7 @@
         <v>139</v>
       </c>
       <c r="C128" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D128" t="s">
         <v>26</v>
@@ -6843,7 +7290,7 @@
         <v>137</v>
       </c>
       <c r="F128" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H128" t="str">
         <f t="shared" si="9"/>
@@ -6875,7 +7322,7 @@
         <v>137</v>
       </c>
       <c r="F129" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H129" t="str">
         <f t="shared" si="9"/>
@@ -6898,7 +7345,7 @@
         <v>141</v>
       </c>
       <c r="C130" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6907,7 +7354,7 @@
         <v>144</v>
       </c>
       <c r="F130" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H130" t="str">
         <f t="shared" si="9"/>
@@ -6930,7 +7377,7 @@
         <v>142</v>
       </c>
       <c r="C131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6939,7 +7386,7 @@
         <v>144</v>
       </c>
       <c r="F131" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H131" t="str">
         <f t="shared" si="9"/>
@@ -6962,7 +7409,7 @@
         <v>143</v>
       </c>
       <c r="C132" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6971,7 +7418,7 @@
         <v>144</v>
       </c>
       <c r="F132" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H132" t="str">
         <f t="shared" si="9"/>
@@ -6994,7 +7441,7 @@
         <v>145</v>
       </c>
       <c r="C133" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D133" t="s">
         <v>21</v>
@@ -7003,7 +7450,7 @@
         <v>144</v>
       </c>
       <c r="F133" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H133" t="str">
         <f t="shared" ref="H133:H196" si="12">IF(J133=1,L133&amp;".png","")</f>
@@ -7035,7 +7482,7 @@
         <v>144</v>
       </c>
       <c r="F134" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H134" t="str">
         <f t="shared" si="12"/>
@@ -7067,7 +7514,7 @@
         <v>144</v>
       </c>
       <c r="F135" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H135" t="str">
         <f t="shared" si="12"/>
@@ -7090,7 +7537,7 @@
         <v>148</v>
       </c>
       <c r="C136" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D136" t="s">
         <v>21</v>
@@ -7099,7 +7546,7 @@
         <v>144</v>
       </c>
       <c r="F136" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H136" t="str">
         <f t="shared" si="12"/>
@@ -7122,7 +7569,7 @@
         <v>149</v>
       </c>
       <c r="C137" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D137" t="s">
         <v>21</v>
@@ -7131,7 +7578,7 @@
         <v>144</v>
       </c>
       <c r="F137" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H137" t="str">
         <f t="shared" si="12"/>
@@ -7157,7 +7604,7 @@
         <v>150</v>
       </c>
       <c r="C138" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D138" t="s">
         <v>21</v>
@@ -7166,7 +7613,7 @@
         <v>144</v>
       </c>
       <c r="F138" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H138" t="str">
         <f t="shared" si="12"/>
@@ -7186,7 +7633,7 @@
         <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C139" t="s">
         <v>10</v>
@@ -7198,7 +7645,7 @@
         <v>144</v>
       </c>
       <c r="F139" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H139" t="str">
         <f t="shared" si="12"/>
@@ -7224,7 +7671,7 @@
         <v>151</v>
       </c>
       <c r="C140" t="s">
-        <v>325</v>
+        <v>10</v>
       </c>
       <c r="D140" t="s">
         <v>26</v>
@@ -7233,7 +7680,7 @@
         <v>144</v>
       </c>
       <c r="F140" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H140" t="str">
         <f t="shared" si="12"/>
@@ -7256,7 +7703,7 @@
         <v>152</v>
       </c>
       <c r="C141" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -7265,7 +7712,7 @@
         <v>172</v>
       </c>
       <c r="F141" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H141" t="str">
         <f t="shared" si="12"/>
@@ -7300,7 +7747,7 @@
         <v>172</v>
       </c>
       <c r="F142" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H142" t="str">
         <f t="shared" si="12"/>
@@ -7323,7 +7770,7 @@
         <v>154</v>
       </c>
       <c r="C143" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -7332,7 +7779,7 @@
         <v>172</v>
       </c>
       <c r="F143" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H143" t="str">
         <f t="shared" si="12"/>
@@ -7355,7 +7802,7 @@
         <v>155</v>
       </c>
       <c r="C144" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -7364,7 +7811,7 @@
         <v>172</v>
       </c>
       <c r="F144" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H144" t="str">
         <f t="shared" si="12"/>
@@ -7399,7 +7846,7 @@
         <v>172</v>
       </c>
       <c r="F145" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H145" t="str">
         <f t="shared" si="12"/>
@@ -7422,7 +7869,7 @@
         <v>157</v>
       </c>
       <c r="C146" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D146" t="s">
         <v>21</v>
@@ -7431,7 +7878,7 @@
         <v>172</v>
       </c>
       <c r="F146" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H146" t="str">
         <f t="shared" si="12"/>
@@ -7466,7 +7913,7 @@
         <v>172</v>
       </c>
       <c r="F147" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H147" t="str">
         <f t="shared" si="12"/>
@@ -7489,7 +7936,7 @@
         <v>159</v>
       </c>
       <c r="C148" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D148" t="s">
         <v>21</v>
@@ -7498,7 +7945,7 @@
         <v>172</v>
       </c>
       <c r="F148" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H148" t="str">
         <f t="shared" si="12"/>
@@ -7521,7 +7968,7 @@
         <v>160</v>
       </c>
       <c r="C149" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D149" t="s">
         <v>21</v>
@@ -7530,7 +7977,7 @@
         <v>172</v>
       </c>
       <c r="F149" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H149" t="str">
         <f t="shared" si="12"/>
@@ -7553,7 +8000,7 @@
         <v>161</v>
       </c>
       <c r="C150" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D150" t="s">
         <v>21</v>
@@ -7562,7 +8009,7 @@
         <v>172</v>
       </c>
       <c r="F150" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H150" t="str">
         <f t="shared" si="12"/>
@@ -7597,7 +8044,7 @@
         <v>172</v>
       </c>
       <c r="F151" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H151" t="str">
         <f t="shared" si="12"/>
@@ -7629,7 +8076,7 @@
         <v>172</v>
       </c>
       <c r="F152" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H152" t="str">
         <f t="shared" si="12"/>
@@ -7652,7 +8099,7 @@
         <v>164</v>
       </c>
       <c r="C153" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D153" t="s">
         <v>26</v>
@@ -7661,7 +8108,7 @@
         <v>172</v>
       </c>
       <c r="F153" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H153" t="str">
         <f t="shared" si="12"/>
@@ -7687,7 +8134,7 @@
         <v>165</v>
       </c>
       <c r="C154" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D154" t="s">
         <v>26</v>
@@ -7696,7 +8143,7 @@
         <v>172</v>
       </c>
       <c r="F154" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H154" t="str">
         <f t="shared" si="12"/>
@@ -7725,7 +8172,7 @@
         <v>166</v>
       </c>
       <c r="C155" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D155" t="s">
         <v>26</v>
@@ -7734,7 +8181,7 @@
         <v>172</v>
       </c>
       <c r="F155" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H155" t="str">
         <f t="shared" si="12"/>
@@ -7757,7 +8204,7 @@
         <v>167</v>
       </c>
       <c r="C156" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D156" t="s">
         <v>26</v>
@@ -7766,7 +8213,7 @@
         <v>172</v>
       </c>
       <c r="F156" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H156" t="str">
         <f t="shared" si="12"/>
@@ -7798,7 +8245,7 @@
         <v>172</v>
       </c>
       <c r="F157" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H157" t="str">
         <f t="shared" si="12"/>
@@ -7821,7 +8268,7 @@
         <v>169</v>
       </c>
       <c r="C158" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D158" t="s">
         <v>26</v>
@@ -7830,7 +8277,7 @@
         <v>172</v>
       </c>
       <c r="F158" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H158" t="str">
         <f t="shared" si="12"/>
@@ -7853,7 +8300,7 @@
         <v>170</v>
       </c>
       <c r="C159" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D159" t="s">
         <v>26</v>
@@ -7862,7 +8309,7 @@
         <v>172</v>
       </c>
       <c r="F159" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H159" t="str">
         <f t="shared" si="12"/>
@@ -7885,7 +8332,7 @@
         <v>171</v>
       </c>
       <c r="C160" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D160" t="s">
         <v>26</v>
@@ -7894,7 +8341,7 @@
         <v>172</v>
       </c>
       <c r="F160" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H160" t="str">
         <f t="shared" si="12"/>
@@ -7929,7 +8376,7 @@
         <v>184</v>
       </c>
       <c r="F161" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H161" t="str">
         <f t="shared" si="12"/>
@@ -7961,7 +8408,7 @@
         <v>184</v>
       </c>
       <c r="F162" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H162" t="str">
         <f t="shared" si="12"/>
@@ -7984,7 +8431,7 @@
         <v>175</v>
       </c>
       <c r="C163" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7993,7 +8440,7 @@
         <v>184</v>
       </c>
       <c r="F163" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H163" t="str">
         <f t="shared" si="12"/>
@@ -8019,7 +8466,7 @@
         <v>176</v>
       </c>
       <c r="C164" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D164" t="s">
         <v>21</v>
@@ -8028,7 +8475,7 @@
         <v>184</v>
       </c>
       <c r="F164" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H164" t="str">
         <f t="shared" si="12"/>
@@ -8051,7 +8498,7 @@
         <v>177</v>
       </c>
       <c r="C165" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D165" t="s">
         <v>21</v>
@@ -8060,7 +8507,7 @@
         <v>184</v>
       </c>
       <c r="F165" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H165" t="str">
         <f t="shared" si="12"/>
@@ -8083,7 +8530,7 @@
         <v>178</v>
       </c>
       <c r="C166" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D166" t="s">
         <v>21</v>
@@ -8092,7 +8539,7 @@
         <v>184</v>
       </c>
       <c r="F166" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H166" t="str">
         <f t="shared" si="12"/>
@@ -8118,7 +8565,7 @@
         <v>179</v>
       </c>
       <c r="C167" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D167" t="s">
         <v>21</v>
@@ -8127,7 +8574,7 @@
         <v>184</v>
       </c>
       <c r="F167" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H167" t="str">
         <f t="shared" si="12"/>
@@ -8153,7 +8600,7 @@
         <v>180</v>
       </c>
       <c r="C168" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D168" t="s">
         <v>21</v>
@@ -8162,7 +8609,7 @@
         <v>184</v>
       </c>
       <c r="F168" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H168" t="str">
         <f t="shared" si="12"/>
@@ -8197,7 +8644,7 @@
         <v>184</v>
       </c>
       <c r="F169" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H169" t="str">
         <f t="shared" si="12"/>
@@ -8220,7 +8667,7 @@
         <v>182</v>
       </c>
       <c r="C170" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D170" t="s">
         <v>21</v>
@@ -8229,7 +8676,7 @@
         <v>184</v>
       </c>
       <c r="F170" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H170" t="str">
         <f t="shared" si="12"/>
@@ -8255,7 +8702,7 @@
         <v>183</v>
       </c>
       <c r="C171" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D171" t="s">
         <v>21</v>
@@ -8264,7 +8711,7 @@
         <v>184</v>
       </c>
       <c r="F171" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H171" t="str">
         <f t="shared" si="12"/>
@@ -8287,7 +8734,7 @@
         <v>185</v>
       </c>
       <c r="C172" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D172" t="s">
         <v>26</v>
@@ -8296,7 +8743,7 @@
         <v>184</v>
       </c>
       <c r="F172" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H172" t="str">
         <f t="shared" si="12"/>
@@ -8319,7 +8766,7 @@
         <v>186</v>
       </c>
       <c r="C173" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D173" t="s">
         <v>26</v>
@@ -8328,7 +8775,7 @@
         <v>184</v>
       </c>
       <c r="F173" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H173" t="str">
         <f t="shared" si="12"/>
@@ -8354,7 +8801,7 @@
         <v>187</v>
       </c>
       <c r="C174" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D174" t="s">
         <v>26</v>
@@ -8363,7 +8810,7 @@
         <v>184</v>
       </c>
       <c r="F174" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H174" t="str">
         <f t="shared" si="12"/>
@@ -8389,7 +8836,7 @@
         <v>188</v>
       </c>
       <c r="C175" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D175" t="s">
         <v>26</v>
@@ -8398,7 +8845,7 @@
         <v>184</v>
       </c>
       <c r="F175" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H175" t="str">
         <f t="shared" si="12"/>
@@ -8430,7 +8877,7 @@
         <v>184</v>
       </c>
       <c r="F176" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H176" t="str">
         <f t="shared" si="12"/>
@@ -8453,7 +8900,7 @@
         <v>190</v>
       </c>
       <c r="C177" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -8462,7 +8909,7 @@
         <v>199</v>
       </c>
       <c r="F177" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H177" t="str">
         <f t="shared" si="12"/>
@@ -8488,7 +8935,7 @@
         <v>191</v>
       </c>
       <c r="C178" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -8497,7 +8944,7 @@
         <v>199</v>
       </c>
       <c r="F178" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H178" t="str">
         <f t="shared" si="12"/>
@@ -8520,7 +8967,7 @@
         <v>192</v>
       </c>
       <c r="C179" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -8529,7 +8976,7 @@
         <v>199</v>
       </c>
       <c r="F179" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H179" t="str">
         <f t="shared" si="12"/>
@@ -8552,7 +8999,7 @@
         <v>193</v>
       </c>
       <c r="C180" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -8561,7 +9008,7 @@
         <v>199</v>
       </c>
       <c r="F180" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H180" t="str">
         <f t="shared" si="12"/>
@@ -8584,7 +9031,7 @@
         <v>194</v>
       </c>
       <c r="C181" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -8593,7 +9040,7 @@
         <v>199</v>
       </c>
       <c r="F181" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H181" t="str">
         <f t="shared" si="12"/>
@@ -8616,7 +9063,7 @@
         <v>195</v>
       </c>
       <c r="C182" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -8625,7 +9072,7 @@
         <v>199</v>
       </c>
       <c r="F182" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H182" t="str">
         <f t="shared" si="12"/>
@@ -8648,7 +9095,7 @@
         <v>196</v>
       </c>
       <c r="C183" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -8657,7 +9104,7 @@
         <v>199</v>
       </c>
       <c r="F183" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H183" t="str">
         <f t="shared" si="12"/>
@@ -8683,7 +9130,7 @@
         <v>197</v>
       </c>
       <c r="C184" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -8692,7 +9139,7 @@
         <v>199</v>
       </c>
       <c r="F184" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H184" t="str">
         <f t="shared" si="12"/>
@@ -8724,7 +9171,7 @@
         <v>199</v>
       </c>
       <c r="F185" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H185" t="str">
         <f t="shared" si="12"/>
@@ -8747,7 +9194,7 @@
         <v>200</v>
       </c>
       <c r="C186" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D186" t="s">
         <v>21</v>
@@ -8756,7 +9203,7 @@
         <v>199</v>
       </c>
       <c r="F186" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H186" t="str">
         <f t="shared" si="12"/>
@@ -8791,7 +9238,7 @@
         <v>199</v>
       </c>
       <c r="F187" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H187" t="str">
         <f t="shared" si="12"/>
@@ -8814,7 +9261,7 @@
         <v>202</v>
       </c>
       <c r="C188" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D188" t="s">
         <v>21</v>
@@ -8823,7 +9270,7 @@
         <v>199</v>
       </c>
       <c r="F188" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H188" t="str">
         <f t="shared" si="12"/>
@@ -8849,7 +9296,7 @@
         <v>203</v>
       </c>
       <c r="C189" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D189" t="s">
         <v>21</v>
@@ -8858,7 +9305,7 @@
         <v>199</v>
       </c>
       <c r="F189" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H189" t="str">
         <f t="shared" si="12"/>
@@ -8881,7 +9328,7 @@
         <v>204</v>
       </c>
       <c r="C190" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D190" t="s">
         <v>21</v>
@@ -8890,7 +9337,7 @@
         <v>199</v>
       </c>
       <c r="F190" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H190" t="str">
         <f t="shared" si="12"/>
@@ -8913,7 +9360,7 @@
         <v>205</v>
       </c>
       <c r="C191" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D191" t="s">
         <v>21</v>
@@ -8922,7 +9369,7 @@
         <v>199</v>
       </c>
       <c r="F191" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H191" t="str">
         <f t="shared" si="12"/>
@@ -8945,7 +9392,7 @@
         <v>206</v>
       </c>
       <c r="C192" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D192" t="s">
         <v>21</v>
@@ -8954,7 +9401,7 @@
         <v>199</v>
       </c>
       <c r="F192" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H192" t="str">
         <f t="shared" si="12"/>
@@ -8977,7 +9424,7 @@
         <v>207</v>
       </c>
       <c r="C193" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D193" t="s">
         <v>26</v>
@@ -8986,7 +9433,7 @@
         <v>199</v>
       </c>
       <c r="F193" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H193" t="str">
         <f t="shared" si="12"/>
@@ -9009,7 +9456,7 @@
         <v>208</v>
       </c>
       <c r="C194" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D194" t="s">
         <v>26</v>
@@ -9018,7 +9465,7 @@
         <v>199</v>
       </c>
       <c r="F194" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H194" t="str">
         <f t="shared" si="12"/>
@@ -9041,7 +9488,7 @@
         <v>209</v>
       </c>
       <c r="C195" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D195" t="s">
         <v>26</v>
@@ -9050,7 +9497,7 @@
         <v>199</v>
       </c>
       <c r="F195" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H195" t="str">
         <f t="shared" si="12"/>
@@ -9073,7 +9520,7 @@
         <v>210</v>
       </c>
       <c r="C196" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D196" t="s">
         <v>26</v>
@@ -9082,7 +9529,7 @@
         <v>199</v>
       </c>
       <c r="F196" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H196" t="str">
         <f t="shared" si="12"/>
@@ -9108,7 +9555,7 @@
         <v>211</v>
       </c>
       <c r="C197" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D197" t="s">
         <v>26</v>
@@ -9117,7 +9564,7 @@
         <v>199</v>
       </c>
       <c r="F197" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H197" t="str">
         <f t="shared" ref="H197:H260" si="15">IF(J197=1,L197&amp;".png","")</f>
@@ -9140,7 +9587,7 @@
         <v>212</v>
       </c>
       <c r="C198" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D198" t="s">
         <v>26</v>
@@ -9149,7 +9596,7 @@
         <v>199</v>
       </c>
       <c r="F198" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H198" t="str">
         <f t="shared" si="15"/>
@@ -9175,7 +9622,7 @@
         <v>213</v>
       </c>
       <c r="C199" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D199" t="s">
         <v>26</v>
@@ -9184,7 +9631,7 @@
         <v>199</v>
       </c>
       <c r="F199" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H199" t="str">
         <f t="shared" si="15"/>
@@ -9207,7 +9654,7 @@
         <v>214</v>
       </c>
       <c r="C200" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D200" t="s">
         <v>26</v>
@@ -9216,7 +9663,7 @@
         <v>199</v>
       </c>
       <c r="F200" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H200" t="str">
         <f t="shared" si="15"/>
@@ -9239,7 +9686,7 @@
         <v>215</v>
       </c>
       <c r="C201" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -9248,7 +9695,7 @@
         <v>222</v>
       </c>
       <c r="F201" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H201" t="str">
         <f t="shared" si="15"/>
@@ -9274,7 +9721,7 @@
         <v>216</v>
       </c>
       <c r="C202" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -9283,7 +9730,7 @@
         <v>222</v>
       </c>
       <c r="F202" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H202" t="str">
         <f t="shared" si="15"/>
@@ -9306,7 +9753,7 @@
         <v>217</v>
       </c>
       <c r="C203" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -9315,7 +9762,7 @@
         <v>222</v>
       </c>
       <c r="F203" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H203" t="str">
         <f t="shared" si="15"/>
@@ -9338,7 +9785,7 @@
         <v>218</v>
       </c>
       <c r="C204" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -9347,7 +9794,7 @@
         <v>222</v>
       </c>
       <c r="F204" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H204" t="str">
         <f t="shared" si="15"/>
@@ -9370,7 +9817,7 @@
         <v>219</v>
       </c>
       <c r="C205" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -9379,7 +9826,7 @@
         <v>222</v>
       </c>
       <c r="F205" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H205" t="str">
         <f t="shared" si="15"/>
@@ -9408,7 +9855,7 @@
         <v>220</v>
       </c>
       <c r="C206" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -9417,7 +9864,7 @@
         <v>222</v>
       </c>
       <c r="F206" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H206" t="str">
         <f t="shared" si="15"/>
@@ -9440,7 +9887,7 @@
         <v>221</v>
       </c>
       <c r="C207" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -9449,7 +9896,7 @@
         <v>222</v>
       </c>
       <c r="F207" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H207" t="str">
         <f t="shared" si="15"/>
@@ -9475,7 +9922,7 @@
         <v>223</v>
       </c>
       <c r="C208" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D208" t="s">
         <v>21</v>
@@ -9484,7 +9931,7 @@
         <v>222</v>
       </c>
       <c r="F208" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H208" t="str">
         <f t="shared" si="15"/>
@@ -9510,7 +9957,7 @@
         <v>224</v>
       </c>
       <c r="C209" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D209" t="s">
         <v>21</v>
@@ -9519,7 +9966,7 @@
         <v>222</v>
       </c>
       <c r="F209" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H209" t="str">
         <f t="shared" si="15"/>
@@ -9551,7 +9998,7 @@
         <v>222</v>
       </c>
       <c r="F210" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H210" t="str">
         <f t="shared" si="15"/>
@@ -9574,7 +10021,7 @@
         <v>226</v>
       </c>
       <c r="C211" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D211" t="s">
         <v>21</v>
@@ -9583,7 +10030,7 @@
         <v>222</v>
       </c>
       <c r="F211" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H211" t="str">
         <f t="shared" si="15"/>
@@ -9606,7 +10053,7 @@
         <v>227</v>
       </c>
       <c r="C212" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D212" t="s">
         <v>21</v>
@@ -9615,7 +10062,7 @@
         <v>222</v>
       </c>
       <c r="F212" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H212" t="str">
         <f t="shared" si="15"/>
@@ -9650,7 +10097,7 @@
         <v>222</v>
       </c>
       <c r="F213" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H213" t="str">
         <f t="shared" si="15"/>
@@ -9673,7 +10120,7 @@
         <v>229</v>
       </c>
       <c r="C214" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D214" t="s">
         <v>21</v>
@@ -9682,7 +10129,7 @@
         <v>222</v>
       </c>
       <c r="F214" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="H214" t="str">
         <f t="shared" si="15"/>
@@ -9708,7 +10155,7 @@
         <v>230</v>
       </c>
       <c r="C215" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D215" t="s">
         <v>21</v>
@@ -9717,7 +10164,7 @@
         <v>222</v>
       </c>
       <c r="F215" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H215" t="str">
         <f t="shared" si="15"/>
@@ -9749,7 +10196,7 @@
         <v>222</v>
       </c>
       <c r="F216" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H216" t="str">
         <f t="shared" si="15"/>
@@ -9772,7 +10219,7 @@
         <v>232</v>
       </c>
       <c r="C217" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D217" t="s">
         <v>21</v>
@@ -9781,7 +10228,7 @@
         <v>222</v>
       </c>
       <c r="F217" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H217" t="str">
         <f t="shared" si="15"/>
@@ -9804,7 +10251,7 @@
         <v>233</v>
       </c>
       <c r="C218" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D218" t="s">
         <v>26</v>
@@ -9813,7 +10260,7 @@
         <v>222</v>
       </c>
       <c r="F218" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H218" t="str">
         <f t="shared" si="15"/>
@@ -9839,7 +10286,7 @@
         <v>234</v>
       </c>
       <c r="C219" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D219" t="s">
         <v>26</v>
@@ -9848,7 +10295,7 @@
         <v>222</v>
       </c>
       <c r="F219" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H219" t="str">
         <f t="shared" si="15"/>
@@ -9874,7 +10321,7 @@
         <v>235</v>
       </c>
       <c r="C220" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D220" t="s">
         <v>26</v>
@@ -9883,7 +10330,7 @@
         <v>222</v>
       </c>
       <c r="F220" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="H220" t="str">
         <f t="shared" si="15"/>
@@ -9909,7 +10356,7 @@
         <v>236</v>
       </c>
       <c r="C221" t="s">
-        <v>327</v>
+        <v>10</v>
       </c>
       <c r="D221" t="s">
         <v>26</v>
@@ -9918,7 +10365,7 @@
         <v>222</v>
       </c>
       <c r="F221" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H221" t="str">
         <f t="shared" si="15"/>
@@ -9944,7 +10391,7 @@
         <v>237</v>
       </c>
       <c r="C222" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D222" t="s">
         <v>26</v>
@@ -9953,7 +10400,7 @@
         <v>222</v>
       </c>
       <c r="F222" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H222" t="str">
         <f t="shared" si="15"/>
@@ -9988,7 +10435,7 @@
         <v>222</v>
       </c>
       <c r="F223" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="H223" t="str">
         <f t="shared" si="15"/>
@@ -10014,7 +10461,7 @@
         <v>239</v>
       </c>
       <c r="C224" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D224" t="s">
         <v>26</v>
@@ -10023,7 +10470,7 @@
         <v>222</v>
       </c>
       <c r="F224" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H224" t="str">
         <f t="shared" si="15"/>
@@ -10049,7 +10496,7 @@
         <v>240</v>
       </c>
       <c r="C225" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D225" t="s">
         <v>26</v>
@@ -10058,7 +10505,7 @@
         <v>222</v>
       </c>
       <c r="F225" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H225" t="str">
         <f t="shared" si="15"/>
@@ -10084,16 +10531,16 @@
         <v>241</v>
       </c>
       <c r="C226" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
       </c>
       <c r="E226" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F226" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H226" t="str">
         <f t="shared" si="15"/>
@@ -10116,16 +10563,16 @@
         <v>242</v>
       </c>
       <c r="C227" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
       </c>
       <c r="E227" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F227" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H227" t="str">
         <f t="shared" si="15"/>
@@ -10148,16 +10595,16 @@
         <v>243</v>
       </c>
       <c r="C228" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
       </c>
       <c r="E228" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F228" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H228" t="str">
         <f t="shared" si="15"/>
@@ -10177,19 +10624,19 @@
         <v>226</v>
       </c>
       <c r="B229" t="s">
-        <v>244</v>
+        <v>672</v>
       </c>
       <c r="C229" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
       </c>
       <c r="E229" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F229" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H229" t="str">
         <f t="shared" si="15"/>
@@ -10209,19 +10656,19 @@
         <v>227</v>
       </c>
       <c r="B230" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C230" t="s">
-        <v>10</v>
+        <v>322</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
       </c>
       <c r="E230" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F230" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H230" t="str">
         <f t="shared" si="15"/>
@@ -10241,19 +10688,19 @@
         <v>228</v>
       </c>
       <c r="B231" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C231" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
       </c>
       <c r="E231" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F231" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H231" t="str">
         <f t="shared" si="15"/>
@@ -10273,19 +10720,19 @@
         <v>229</v>
       </c>
       <c r="B232" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C232" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
       </c>
       <c r="E232" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F232" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H232" t="str">
         <f t="shared" si="15"/>
@@ -10305,7 +10752,7 @@
         <v>230</v>
       </c>
       <c r="B233" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C233" t="s">
         <v>10</v>
@@ -10314,10 +10761,10 @@
         <v>7</v>
       </c>
       <c r="E233" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F233" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H233" t="str">
         <f t="shared" si="15"/>
@@ -10337,19 +10784,19 @@
         <v>231</v>
       </c>
       <c r="B234" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C234" t="s">
-        <v>328</v>
+        <v>10</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
       </c>
       <c r="E234" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F234" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H234" t="str">
         <f t="shared" si="15"/>
@@ -10369,19 +10816,19 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C235" t="s">
-        <v>312</v>
+        <v>10</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
       </c>
       <c r="E235" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F235" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H235" t="str">
         <f t="shared" si="15"/>
@@ -10404,19 +10851,19 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C236" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D236" t="s">
         <v>21</v>
       </c>
       <c r="E236" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F236" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H236" t="str">
         <f t="shared" si="15"/>
@@ -10436,19 +10883,19 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C237" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D237" t="s">
         <v>21</v>
       </c>
       <c r="E237" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F237" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H237" t="str">
         <f t="shared" si="15"/>
@@ -10468,19 +10915,19 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C238" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D238" t="s">
         <v>21</v>
       </c>
       <c r="E238" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F238" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H238" t="str">
         <f t="shared" si="15"/>
@@ -10503,19 +10950,19 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C239" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D239" t="s">
         <v>21</v>
       </c>
       <c r="E239" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F239" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H239" t="str">
         <f t="shared" si="15"/>
@@ -10538,19 +10985,19 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C240" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D240" t="s">
         <v>21</v>
       </c>
       <c r="E240" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F240" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H240" t="str">
         <f t="shared" si="15"/>
@@ -10573,7 +11020,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C241" t="s">
         <v>10</v>
@@ -10582,10 +11029,10 @@
         <v>21</v>
       </c>
       <c r="E241" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F241" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H241" t="str">
         <f t="shared" si="15"/>
@@ -10605,7 +11052,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C242" t="s">
         <v>10</v>
@@ -10614,10 +11061,10 @@
         <v>21</v>
       </c>
       <c r="E242" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F242" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H242" t="str">
         <f t="shared" si="15"/>
@@ -10637,19 +11084,19 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C243" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D243" t="s">
         <v>21</v>
       </c>
       <c r="E243" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F243" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H243" t="str">
         <f t="shared" si="15"/>
@@ -10669,19 +11116,19 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C244" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D244" t="s">
         <v>21</v>
       </c>
       <c r="E244" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F244" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H244" t="str">
         <f t="shared" si="15"/>
@@ -10701,19 +11148,19 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C245" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D245" t="s">
         <v>26</v>
       </c>
       <c r="E245" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F245" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H245" t="str">
         <f t="shared" si="15"/>
@@ -10736,19 +11183,19 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D246" t="s">
         <v>26</v>
       </c>
       <c r="E246" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F246" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H246" t="str">
         <f t="shared" si="15"/>
@@ -10768,19 +11215,19 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C247" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D247" t="s">
         <v>26</v>
       </c>
       <c r="E247" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F247" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H247" t="str">
         <f t="shared" si="15"/>
@@ -10800,19 +11247,19 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C248" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D248" t="s">
         <v>26</v>
       </c>
       <c r="E248" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F248" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H248" t="str">
         <f t="shared" si="15"/>
@@ -10832,19 +11279,19 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C249" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D249" t="s">
         <v>26</v>
       </c>
       <c r="E249" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F249" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H249" t="str">
         <f t="shared" si="15"/>
@@ -10867,19 +11314,19 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C250" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D250" t="s">
         <v>26</v>
       </c>
       <c r="E250" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F250" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H250" t="str">
         <f t="shared" si="15"/>
@@ -10902,19 +11349,19 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C251" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D251" t="s">
         <v>26</v>
       </c>
       <c r="E251" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F251" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H251" t="str">
         <f t="shared" si="15"/>
@@ -10934,7 +11381,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C252" t="s">
         <v>10</v>
@@ -10943,10 +11390,10 @@
         <v>26</v>
       </c>
       <c r="E252" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F252" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H252" t="str">
         <f t="shared" si="15"/>
@@ -10966,19 +11413,19 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C253" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D253" t="s">
         <v>26</v>
       </c>
       <c r="E253" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F253" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H253" t="str">
         <f t="shared" si="15"/>
@@ -10998,19 +11445,19 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C254" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
       </c>
       <c r="E254" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F254" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H254" t="str">
         <f t="shared" si="15"/>
@@ -11033,19 +11480,19 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C255" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
       </c>
       <c r="E255" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F255" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H255" t="str">
         <f t="shared" si="15"/>
@@ -11065,19 +11512,19 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C256" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
       </c>
       <c r="E256" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F256" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H256" t="str">
         <f t="shared" si="15"/>
@@ -11097,19 +11544,19 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C257" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
       </c>
       <c r="E257" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F257" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H257" t="str">
         <f t="shared" si="15"/>
@@ -11129,19 +11576,19 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C258" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
       </c>
       <c r="E258" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F258" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H258" t="str">
         <f t="shared" si="15"/>
@@ -11164,19 +11611,19 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C259" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
       </c>
       <c r="E259" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F259" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H259" t="str">
         <f t="shared" si="15"/>
@@ -11196,19 +11643,19 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C260" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D260" t="s">
         <v>21</v>
       </c>
       <c r="E260" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F260" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H260" t="str">
         <f t="shared" si="15"/>
@@ -11231,19 +11678,19 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C261" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D261" t="s">
         <v>21</v>
       </c>
       <c r="E261" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F261" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="H261" t="str">
         <f t="shared" ref="H261:H300" si="18">IF(J261=1,L261&amp;".png","")</f>
@@ -11254,7 +11701,7 @@
         <v/>
       </c>
       <c r="L261">
-        <f t="shared" ref="L261:L300" si="20">1000+A261</f>
+        <f t="shared" ref="L261:L302" si="20">1000+A261</f>
         <v>1259</v>
       </c>
     </row>
@@ -11263,19 +11710,19 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C262" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D262" t="s">
         <v>21</v>
       </c>
       <c r="E262" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F262" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="H262" t="str">
         <f t="shared" si="18"/>
@@ -11295,19 +11742,19 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C263" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D263" t="s">
         <v>21</v>
       </c>
       <c r="E263" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F263" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H263" t="str">
         <f t="shared" si="18"/>
@@ -11327,19 +11774,19 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C264" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D264" t="s">
         <v>21</v>
       </c>
       <c r="E264" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F264" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H264" t="str">
         <f t="shared" si="18"/>
@@ -11359,7 +11806,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C265" t="s">
         <v>10</v>
@@ -11368,10 +11815,10 @@
         <v>21</v>
       </c>
       <c r="E265" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F265" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H265" t="str">
         <f t="shared" si="18"/>
@@ -11391,19 +11838,19 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C266" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D266" t="s">
         <v>21</v>
       </c>
       <c r="E266" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F266" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H266" t="str">
         <f t="shared" si="18"/>
@@ -11423,19 +11870,19 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C267" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D267" t="s">
         <v>21</v>
       </c>
       <c r="E267" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F267" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="H267" t="str">
         <f t="shared" si="18"/>
@@ -11455,19 +11902,19 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C268" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D268" t="s">
         <v>21</v>
       </c>
       <c r="E268" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F268" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H268" t="str">
         <f t="shared" si="18"/>
@@ -11487,19 +11934,19 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C269" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D269" t="s">
         <v>21</v>
       </c>
       <c r="E269" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F269" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H269" t="str">
         <f t="shared" si="18"/>
@@ -11519,19 +11966,19 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C270" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D270" t="s">
         <v>21</v>
       </c>
       <c r="E270" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F270" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H270" t="str">
         <f t="shared" si="18"/>
@@ -11551,7 +11998,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C271" t="s">
         <v>10</v>
@@ -11560,10 +12007,10 @@
         <v>26</v>
       </c>
       <c r="E271" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F271" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H271" t="str">
         <f t="shared" si="18"/>
@@ -11583,19 +12030,19 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>289</v>
+        <v>646</v>
       </c>
       <c r="C272" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D272" t="s">
         <v>26</v>
       </c>
       <c r="E272" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F272" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H272" t="str">
         <f t="shared" si="18"/>
@@ -11615,19 +12062,19 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C273" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D273" t="s">
         <v>26</v>
       </c>
       <c r="E273" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F273" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H273" t="str">
         <f t="shared" si="18"/>
@@ -11650,19 +12097,19 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C274" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D274" t="s">
         <v>26</v>
       </c>
       <c r="E274" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F274" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H274" t="str">
         <f t="shared" si="18"/>
@@ -11682,19 +12129,19 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C275" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D275" t="s">
         <v>26</v>
       </c>
       <c r="E275" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F275" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H275" t="str">
         <f t="shared" si="18"/>
@@ -11714,19 +12161,19 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C276" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D276" t="s">
         <v>26</v>
       </c>
       <c r="E276" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F276" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H276" t="str">
         <f t="shared" si="18"/>
@@ -11749,19 +12196,19 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C277" t="s">
-        <v>328</v>
+        <v>10</v>
       </c>
       <c r="D277" t="s">
         <v>26</v>
       </c>
       <c r="E277" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F277" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H277" t="str">
         <f t="shared" si="18"/>
@@ -11781,7 +12228,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C278" t="s">
         <v>10</v>
@@ -11790,10 +12237,10 @@
         <v>26</v>
       </c>
       <c r="E278" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F278" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H278" t="str">
         <f t="shared" si="18"/>
@@ -11813,19 +12260,19 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C279" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D279" t="s">
         <v>26</v>
       </c>
       <c r="E279" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F279" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H279" t="str">
         <f t="shared" si="18"/>
@@ -11845,7 +12292,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C280" t="s">
         <v>10</v>
@@ -11854,10 +12301,10 @@
         <v>26</v>
       </c>
       <c r="E280" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F280" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H280" t="str">
         <f t="shared" si="18"/>
@@ -11877,19 +12324,19 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C281" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D281" t="s">
         <v>26</v>
       </c>
       <c r="E281" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F281" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H281" t="str">
         <f t="shared" si="18"/>
@@ -11909,19 +12356,19 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C282" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D282" t="s">
         <v>26</v>
       </c>
       <c r="E282" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F282" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H282" t="str">
         <f t="shared" si="18"/>
@@ -11941,19 +12388,19 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C283" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
       </c>
       <c r="E283" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F283" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H283" t="str">
         <f t="shared" si="18"/>
@@ -11973,19 +12420,19 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C284" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
       </c>
       <c r="E284" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F284" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H284" t="str">
         <f t="shared" si="18"/>
@@ -12005,19 +12452,19 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C285" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D285" t="s">
         <v>21</v>
       </c>
       <c r="E285" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F285" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H285" t="str">
         <f t="shared" si="18"/>
@@ -12040,19 +12487,19 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C286" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D286" t="s">
         <v>21</v>
       </c>
       <c r="E286" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F286" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="H286" t="str">
         <f t="shared" si="18"/>
@@ -12072,19 +12519,19 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C287" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D287" t="s">
         <v>21</v>
       </c>
       <c r="E287" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F287" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H287" t="str">
         <f t="shared" si="18"/>
@@ -12104,19 +12551,19 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C288" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D288" t="s">
         <v>26</v>
       </c>
       <c r="E288" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F288" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H288" t="str">
         <f t="shared" si="18"/>
@@ -12136,19 +12583,19 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C289" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D289" t="s">
         <v>26</v>
       </c>
       <c r="E289" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F289" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H289" t="str">
         <f t="shared" si="18"/>
@@ -12168,19 +12615,19 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C290" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D290" t="s">
         <v>26</v>
       </c>
       <c r="E290" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F290" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H290" t="str">
         <f t="shared" si="18"/>
@@ -12200,7 +12647,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C291" t="s">
         <v>10</v>
@@ -12209,10 +12656,10 @@
         <v>26</v>
       </c>
       <c r="E291" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F291" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H291" t="str">
         <f t="shared" si="18"/>
@@ -12232,19 +12679,19 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C292" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D292" t="s">
         <v>26</v>
       </c>
       <c r="E292" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F292" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H292" t="str">
         <f t="shared" si="18"/>
@@ -12264,19 +12711,19 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C293" t="s">
-        <v>328</v>
+        <v>10</v>
       </c>
       <c r="D293" t="s">
         <v>26</v>
       </c>
       <c r="E293" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F293" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H293" t="str">
         <f t="shared" si="18"/>
@@ -12296,10 +12743,10 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C294" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -12308,7 +12755,7 @@
         <v>90</v>
       </c>
       <c r="F294" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H294" t="str">
         <f t="shared" si="18"/>
@@ -12328,19 +12775,19 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C295" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D295" t="s">
         <v>21</v>
       </c>
       <c r="E295" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F295" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H295" t="str">
         <f t="shared" si="18"/>
@@ -12360,19 +12807,19 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C296" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D296" t="s">
         <v>21</v>
       </c>
       <c r="E296" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F296" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H296" t="str">
         <f t="shared" si="18"/>
@@ -12392,19 +12839,19 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C297" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D297" t="s">
         <v>21</v>
       </c>
       <c r="E297" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F297" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H297" t="str">
         <f t="shared" si="18"/>
@@ -12424,10 +12871,10 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C298" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D298" t="s">
         <v>26</v>
@@ -12436,7 +12883,7 @@
         <v>222</v>
       </c>
       <c r="F298" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H298" t="str">
         <f t="shared" si="18"/>
@@ -12459,19 +12906,19 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C299" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D299" t="s">
         <v>26</v>
       </c>
       <c r="E299" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F299" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H299" t="str">
         <f t="shared" si="18"/>
@@ -12491,19 +12938,19 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
+        <v>634</v>
+      </c>
+      <c r="C300" t="s">
+        <v>635</v>
+      </c>
+      <c r="D300" t="s">
         <v>636</v>
       </c>
-      <c r="C300" t="s">
+      <c r="E300" t="s">
         <v>637</v>
       </c>
-      <c r="D300" t="s">
+      <c r="F300" t="s">
         <v>638</v>
-      </c>
-      <c r="E300" t="s">
-        <v>639</v>
-      </c>
-      <c r="F300" t="s">
-        <v>640</v>
       </c>
       <c r="H300" t="str">
         <f t="shared" si="18"/>
@@ -12519,6 +12966,51 @@
       <c r="L300">
         <f t="shared" si="20"/>
         <v>1298</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301" t="s">
+        <v>641</v>
+      </c>
+      <c r="C301" t="s">
+        <v>310</v>
+      </c>
+      <c r="D301" t="s">
+        <v>639</v>
+      </c>
+      <c r="E301" t="s">
+        <v>184</v>
+      </c>
+      <c r="F301" t="s">
+        <v>640</v>
+      </c>
+      <c r="L301">
+        <f t="shared" si="20"/>
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302" t="s">
+        <v>642</v>
+      </c>
+      <c r="D302" t="s">
+        <v>643</v>
+      </c>
+      <c r="E302" t="s">
+        <v>644</v>
+      </c>
+      <c r="F302" t="s">
+        <v>645</v>
+      </c>
+      <c r="L302">
+        <f t="shared" si="20"/>
+        <v>1300</v>
       </c>
     </row>
   </sheetData>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3583DF3F-68CC-497E-894F-1291128299E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DAEA85-77E3-425A-B185-96075965A526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="688">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2656,6 +2656,62 @@
   <si>
     <t>경콩</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>깅예솔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨나인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yunhee1222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유성민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0티어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goodgame07</t>
+  </si>
+  <si>
+    <t>휘연</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타마양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진서랄까</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rldyal71</t>
+  </si>
+  <si>
+    <t>tamama88</t>
+  </si>
+  <si>
+    <t>janjanoo</t>
   </si>
 </sst>
 </file>
@@ -3037,7 +3093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A2A291-B3BF-4EBE-93A6-386812DCA76D}">
-  <dimension ref="A1:Q302"/>
+  <dimension ref="A1:Q307"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="2" max="2" width="10.9375" bestFit="1" customWidth="1"/>
@@ -6254,7 +6310,7 @@
         <v>106</v>
       </c>
       <c r="C96" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
@@ -8367,7 +8423,7 @@
         <v>173</v>
       </c>
       <c r="C161" t="s">
-        <v>10</v>
+        <v>310</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -11701,7 +11757,7 @@
         <v/>
       </c>
       <c r="L261">
-        <f t="shared" ref="L261:L302" si="20">1000+A261</f>
+        <f t="shared" ref="L261:L307" si="20">1000+A261</f>
         <v>1259</v>
       </c>
     </row>
@@ -12999,6 +13055,9 @@
       <c r="B302" t="s">
         <v>642</v>
       </c>
+      <c r="C302" t="s">
+        <v>325</v>
+      </c>
       <c r="D302" t="s">
         <v>643</v>
       </c>
@@ -13011,6 +13070,126 @@
       <c r="L302">
         <f t="shared" si="20"/>
         <v>1300</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303" t="s">
+        <v>673</v>
+      </c>
+      <c r="C303" t="s">
+        <v>674</v>
+      </c>
+      <c r="D303" t="s">
+        <v>675</v>
+      </c>
+      <c r="E303" t="s">
+        <v>222</v>
+      </c>
+      <c r="F303" t="s">
+        <v>676</v>
+      </c>
+      <c r="L303">
+        <f t="shared" si="20"/>
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304" t="s">
+        <v>677</v>
+      </c>
+      <c r="C304" t="s">
+        <v>325</v>
+      </c>
+      <c r="D304" t="s">
+        <v>678</v>
+      </c>
+      <c r="E304" t="s">
+        <v>679</v>
+      </c>
+      <c r="F304" t="s">
+        <v>680</v>
+      </c>
+      <c r="L304">
+        <f t="shared" si="20"/>
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305" t="s">
+        <v>681</v>
+      </c>
+      <c r="C305" t="s">
+        <v>684</v>
+      </c>
+      <c r="D305" t="s">
+        <v>678</v>
+      </c>
+      <c r="E305" t="s">
+        <v>309</v>
+      </c>
+      <c r="F305" t="s">
+        <v>685</v>
+      </c>
+      <c r="L305">
+        <f t="shared" si="20"/>
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306" t="s">
+        <v>682</v>
+      </c>
+      <c r="C306" t="s">
+        <v>684</v>
+      </c>
+      <c r="D306" t="s">
+        <v>675</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+      <c r="F306" t="s">
+        <v>686</v>
+      </c>
+      <c r="L306">
+        <f t="shared" si="20"/>
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307" t="s">
+        <v>683</v>
+      </c>
+      <c r="C307" t="s">
+        <v>325</v>
+      </c>
+      <c r="D307" t="s">
+        <v>675</v>
+      </c>
+      <c r="E307" t="s">
+        <v>309</v>
+      </c>
+      <c r="F307" t="s">
+        <v>687</v>
+      </c>
+      <c r="L307">
+        <f t="shared" si="20"/>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DAEA85-77E3-425A-B185-96075965A526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70483387-8315-47B0-ABF4-0A0F2752C52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="689">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2712,6 +2712,10 @@
   </si>
   <si>
     <t>janjanoo</t>
+  </si>
+  <si>
+    <t>신세계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3170,7 +3174,7 @@
         <v>328</v>
       </c>
       <c r="G2" s="1">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="H2" t="str">
         <f>IF(J2=1,L2&amp;".png","")</f>
@@ -3891,7 +3895,7 @@
         <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4517,7 +4521,7 @@
         <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>317</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -6342,7 +6346,7 @@
         <v>107</v>
       </c>
       <c r="C97" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D97" t="s">
         <v>26</v>
@@ -6630,7 +6634,7 @@
         <v>116</v>
       </c>
       <c r="C106" t="s">
-        <v>10</v>
+        <v>323</v>
       </c>
       <c r="D106" t="s">
         <v>21</v>
@@ -7529,7 +7533,7 @@
         <v>146</v>
       </c>
       <c r="C134" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D134" t="s">
         <v>21</v>
@@ -8554,7 +8558,7 @@
         <v>177</v>
       </c>
       <c r="C165" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D165" t="s">
         <v>21</v>
@@ -10412,7 +10416,7 @@
         <v>236</v>
       </c>
       <c r="C221" t="s">
-        <v>10</v>
+        <v>321</v>
       </c>
       <c r="D221" t="s">
         <v>26</v>
@@ -13104,7 +13108,7 @@
         <v>677</v>
       </c>
       <c r="C304" t="s">
-        <v>325</v>
+        <v>10</v>
       </c>
       <c r="D304" t="s">
         <v>678</v>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70483387-8315-47B0-ABF4-0A0F2752C52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75FEBF3-E57D-4037-BA35-B147AB3B7F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -3174,7 +3174,7 @@
         <v>328</v>
       </c>
       <c r="G2" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H2" t="str">
         <f>IF(J2=1,L2&amp;".png","")</f>
@@ -4029,7 +4029,7 @@
         <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -10049,7 +10049,7 @@
         <v>225</v>
       </c>
       <c r="C210" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D210" t="s">
         <v>21</v>
@@ -12061,7 +12061,7 @@
         <v>287</v>
       </c>
       <c r="C271" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D271" t="s">
         <v>26</v>
